--- a/output/full_scan/batch_seq6_2026-09-24.xlsx
+++ b/output/full_scan/batch_seq6_2026-09-24.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>940.6006439300454</v>
+        <v>1365.600643930045</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>595</v>
@@ -552,29 +552,29 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>66.66258263349687</v>
+        <v>66.66258263654424</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>20.03638225599065</v>
+        <v>20.03638227562102</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.008072549259758</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0279659066944013</v>
+        <v>0.0279659061983181</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>889</v>
+        <v>1064</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>73.59999999999999</v>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>64.83174482238873</v>
+        <v>64.83174482953652</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>21.49977404795331</v>
+        <v>21.4997740037675</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>8.443961698534848</v>
@@ -627,27 +627,27 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6207</v>
+        <v>6456</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>808.3561010787749</v>
+        <v>986.4580486811648</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>125</v>
+        <v>81.3</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>63.0666189077481</v>
+        <v>71.18692325866445</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>14.68035601941076</v>
+        <v>20.36263272905853</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.897767706804681</v>
+        <v>2.24580486811646</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.320441410625059</v>
+        <v>1.558777395678018</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6214</v>
+        <v>6207</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>778.0837061439793</v>
+        <v>978.3561010787748</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>190.5</v>
+        <v>125</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>68.11406773768275</v>
+        <v>63.0666188986628</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>43.05596083437839</v>
+        <v>14.68035603350259</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.350681376804406</v>
+        <v>1.897767706804681</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-1.098817331444118</v>
+        <v>1.320441410873102</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6291</v>
+        <v>6196</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>776.8305267119989</v>
+        <v>940.6269194686164</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>484</v>
+        <v>565</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>56.07705368769372</v>
+        <v>65.54270116081905</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>28.24656534030377</v>
+        <v>15.66891953482067</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.409165748070089</v>
+        <v>0.9584558643329044</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4303852278363713</v>
+        <v>4.653624494291645</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6225</v>
+        <v>6214</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>761</v>
+        <v>888.0837061439793</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>50.4</v>
+        <v>190.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>43.51236129090329</v>
+        <v>68.11406770902241</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>30.01213485923392</v>
+        <v>43.05596085311367</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>10.36975850628528</v>
+        <v>1.350681376804406</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-3.15608168155113</v>
+        <v>-1.098817331157905</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6271</v>
+        <v>6274</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>729.8220532678628</v>
+        <v>882.0855854405762</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>229</v>
+        <v>1495</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>57.91764611266962</v>
+        <v>56.400107946741</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>24.12880697053987</v>
+        <v>19.34389631197316</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.3509783905401061</v>
+        <v>1.349263704100556</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.2499790629949831</v>
+        <v>12.90742260449349</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6292</v>
+        <v>6182</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>714.7329515153431</v>
+        <v>869.4724465398691</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>67</v>
+        <v>120.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>59.6111060781836</v>
+        <v>58.26573932016866</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>29.83339520938796</v>
+        <v>15.61506634594098</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.5071471822056217</v>
+        <v>1.74736065382166</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.0336552233160023</v>
+        <v>1.446095108044223</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6274</v>
+        <v>6166</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>712.085585440576</v>
+        <v>856.3184997482543</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1495</v>
+        <v>132</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>56.40010795846624</v>
+        <v>63.59559106136845</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>19.34389637187517</v>
+        <v>22.17453390448567</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.349263704100556</v>
+        <v>1.069878972973927</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>12.9074226048751</v>
+        <v>2.69445116942654</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6456</v>
+        <v>6271</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>711.4580486811647</v>
+        <v>839.8220532678628</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>81.3</v>
+        <v>229</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>71.1869232555857</v>
+        <v>57.91764608773407</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>20.36263267812481</v>
+        <v>24.12880708304367</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.24580486811646</v>
+        <v>0.3509783905401061</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>1.558777395697104</v>
+        <v>-0.249979062613372</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6182</v>
+        <v>6257</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>699.4724465398691</v>
+        <v>783.0898562793354</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>120.5</v>
+        <v>243</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>58.26573933493162</v>
+        <v>64.3875813106133</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>15.61506630989532</v>
+        <v>20.97541043626613</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.74736065382166</v>
+        <v>0.9196191487819916</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1.446095107901131</v>
+        <v>3.835269044018928</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6245</v>
+        <v>6291</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>685.7153359639725</v>
+        <v>776.8305267119989</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>85.7</v>
+        <v>484</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>55.81718956190101</v>
+        <v>56.07705364981348</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>20.41421827082376</v>
+        <v>28.24656522959186</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.4982216913324923</v>
+        <v>0.409165748070089</v>
       </c>
       <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.4346386186175548</v>
+        <v>0.4303852299350659</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6173</v>
+        <v>6225</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>683.6060348673063</v>
+        <v>771</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>306.5</v>
+        <v>50.4</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>63.50779682148377</v>
+        <v>43.5123613101049</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>37.54616092655088</v>
+        <v>30.01213485923392</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.5615549729494477</v>
+        <v>10.36975850628528</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.1797555504200474</v>
+        <v>-3.156081681665603</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6227</v>
+        <v>6416</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>682.6440202385866</v>
+        <v>769.0748431689007</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>135.5</v>
+        <v>116.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>64.06823282644743</v>
+        <v>62.65092002827535</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>30.43473398510765</v>
+        <v>30.71079744674877</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.5644020238586532</v>
+        <v>0.2359423414332075</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.439548690263611</v>
+        <v>0.2252700331006494</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6416</v>
+        <v>6426</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>669.0748431689007</v>
+        <v>748.9429054178037</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>116.5</v>
+        <v>389</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>62.65092002491763</v>
+        <v>73.21134644791351</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>30.71079722431378</v>
+        <v>46.69088127013588</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.2359423414332075</v>
+        <v>1.2929223485303</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.2252700329671064</v>
+        <v>5.39644513611394</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6290</v>
+        <v>6224</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>664.5775541717605</v>
+        <v>734.4020503562305</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>274</v>
+        <v>82.2</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>58.42997937345443</v>
+        <v>52.12986569519275</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>28.20794360798656</v>
+        <v>42.62926850747657</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.5005337089655052</v>
+        <v>0.3708707727099934</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.5430680892161792</v>
+        <v>-1.198090568126521</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6196</v>
+        <v>6443</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>650.6269194686189</v>
+        <v>726.5993410751819</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>565</v>
+        <v>28.25</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>65.54270118442618</v>
+        <v>62.63390265223265</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>15.66891957386162</v>
+        <v>23.28980005677465</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.9584558643329044</v>
+        <v>2.259934107518183</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>4.653624494482452</v>
+        <v>0.6575100139948079</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6218</v>
+        <v>6204</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>648.8108282475747</v>
+        <v>723.1294712635267</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>63.6</v>
+        <v>107.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>73.79643634261519</v>
+        <v>64.36927852414901</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>51.93078586803668</v>
+        <v>23.51868146081346</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.3451807893485021</v>
+        <v>1.218678252716549</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1.469175753523721</v>
+        <v>1.361157774871322</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6166</v>
+        <v>6292</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>646.3184997482542</v>
+        <v>714.7329515153431</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>132</v>
+        <v>67</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>63.59559107744856</v>
+        <v>59.6111060781836</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>22.17453380187764</v>
+        <v>29.83339524561203</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.069878972973927</v>
+        <v>0.5071471822056217</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.694451169312074</v>
+        <v>-0.0336552233637077</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6275</v>
+        <v>6228</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>641.2369683980836</v>
+        <v>694</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>45.9</v>
+        <v>18.7</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>53.58585290046296</v>
+        <v>56.17758028652718</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>27.5582420441795</v>
+        <v>15.41856729698002</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.3158218194710098</v>
+        <v>8.688962774626768</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.008119802876267099</v>
+        <v>2.053150232184326</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6224</v>
+        <v>6245</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>634.4020503562303</v>
+        <v>685.7153359639725</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>82.2</v>
+        <v>85.7</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>52.12986568822608</v>
+        <v>55.81718956452371</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>42.62926848737375</v>
+        <v>20.4142183625333</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.3708707727099934</v>
+        <v>0.4982216913324923</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-1.198090568078807</v>
+        <v>0.4346386187129494</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6257</v>
+        <v>6278</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>613.0898562793355</v>
+        <v>684.6191217153681</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>64.38758132625021</v>
+        <v>63.79576574570996</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>20.97541054146426</v>
+        <v>18.39934887542577</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.9196191487819916</v>
+        <v>1.430031148977345</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>3.835269043637304</v>
+        <v>1.789170172527805</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6426</v>
+        <v>6438</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>588.9429054178037</v>
+        <v>683.9215222616863</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>389</v>
+        <v>157.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>73.21134644694749</v>
+        <v>62.08560633698952</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>46.69088122731599</v>
+        <v>18.47983130568164</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.2929223485303</v>
+        <v>2.269757034895909</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>5.396445135865896</v>
+        <v>0.6086841702846781</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6204</v>
+        <v>6173</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>583.1294712635266</v>
+        <v>683.6060348673063</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>107.5</v>
+        <v>306.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>64.36927851778093</v>
+        <v>63.50779681701987</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>23.51868136890087</v>
+        <v>37.54616092363761</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.218678252716549</v>
+        <v>0.5615549729494477</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.361157774775927</v>
+        <v>-0.1797555502959937</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6209</v>
+        <v>6227</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>570.377286429268</v>
+        <v>682.6440202385866</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>79.90000000000001</v>
+        <v>135.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>54.75179758476892</v>
+        <v>64.06823281893976</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>24.25431239172331</v>
+        <v>30.43473403683808</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.5113231867855531</v>
+        <v>0.5644020238586532</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.2460884427437755</v>
+        <v>1.439548690416242</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6438</v>
+        <v>6423</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>543.9215222616858</v>
+        <v>677.3005952777112</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>157.5</v>
+        <v>86.8</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>62.08560635908165</v>
+        <v>61.49437370620001</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>18.47983133928525</v>
+        <v>18.51541259867267</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>2.269757034895909</v>
+        <v>0.6017233650445784</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.6086841698076906</v>
+        <v>0.2766178293574111</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6443</v>
+        <v>6290</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>541.5993410751819</v>
+        <v>664.5775541717605</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>28.25</v>
+        <v>274</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>62.63390270615688</v>
+        <v>58.42997935578455</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>23.28980001697738</v>
+        <v>28.20794361189195</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>2.259934107518183</v>
+        <v>0.5005337089655052</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.6575100139089506</v>
+        <v>0.5430680892161792</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6472</v>
+        <v>6218</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>535.9710232663093</v>
+        <v>648.8108282475747</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>421.5</v>
+        <v>63.6</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>50.27569219145838</v>
+        <v>73.79643634261519</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>21.47895947447875</v>
+        <v>51.93078586803668</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7738837136404555</v>
+        <v>0.3451807893485021</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>1.263825370732253</v>
+        <v>1.469175753523721</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6197</v>
+        <v>6275</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>511.757288614293</v>
+        <v>641.2369683980836</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>320</v>
+        <v>45.9</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>57.56544903934786</v>
+        <v>53.58585285735273</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>14.23362226581263</v>
+        <v>27.55824196537597</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5544628058873015</v>
+        <v>0.3158218194710098</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>2.284717295358724</v>
+        <v>0.0081198029812019</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6423</v>
+        <v>6189</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>507.3005952777112</v>
+        <v>640.72454781075</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>86.8</v>
+        <v>49.2</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>61.49437372921136</v>
+        <v>60.44000170734354</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>18.51541255726263</v>
+        <v>13.67839986329985</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.6017233650445784</v>
+        <v>0.7238251276090925</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.2766178291856951</v>
+        <v>0.2826127597924111</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6266</v>
+        <v>6197</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>505.448080021483</v>
+        <v>626.7572886142935</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>24.9</v>
+        <v>320</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>49.58365127781519</v>
+        <v>57.56544904277526</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>8.538427386320292</v>
+        <v>14.23362223683571</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.6902568812034882</v>
+        <v>0.5544628058873015</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0105393242013103</v>
+        <v>2.284717295549552</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6201</v>
+        <v>6202</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>498.4078607729913</v>
+        <v>623.0894125227733</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>44.7</v>
+        <v>58.2</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,49 +2195,49 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>46.24721724359453</v>
+        <v>53.00848179598765</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>26.99637974488381</v>
+        <v>11.78606048173884</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5352959447436444</v>
+        <v>0.816426638421937</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.0816399017249067</v>
+        <v>0.3757278517633402</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6278</v>
+        <v>6201</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>494.6191217153681</v>
+        <v>608.4078607729914</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>212</v>
+        <v>44.7</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>63.79576574570996</v>
+        <v>46.24721673166113</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>18.39934884175737</v>
+        <v>26.99637978708038</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.430031148977345</v>
+        <v>0.5352959447436444</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>1.789170172432405</v>
+        <v>0.0816399018393856</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6228</v>
+        <v>6270</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>494</v>
+        <v>582.170624986315</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>18.7</v>
+        <v>29.7</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>56.17758028893128</v>
+        <v>54.12259619079699</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>15.41856711274349</v>
+        <v>11.19472339863702</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>8.688962774626768</v>
+        <v>1.106854266184539</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>2.053150231907674</v>
+        <v>0.2093845028315398</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6418</v>
+        <v>6164</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>481.5757285346891</v>
+        <v>579.5083702827676</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>34.55</v>
+        <v>12.25</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>51.76270041597044</v>
+        <v>56.29697327968442</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>29.62341745232738</v>
+        <v>20.87925687214075</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.1094152202160514</v>
+        <v>0.8109296247975909</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.1191691634321584</v>
+        <v>0.1093957968767523</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6164</v>
+        <v>6209</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>474.5083702827677</v>
+        <v>570.377286429268</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>12.25</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>56.29697324636928</v>
+        <v>54.75179759228131</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>20.87925692910236</v>
+        <v>24.25431229264032</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.8109296247975909</v>
+        <v>0.5113231867855531</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.1093957968691212</v>
+        <v>-0.2460884426102092</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6270</v>
+        <v>6210</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>467.170624986315</v>
+        <v>562.2628631187323</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>29.7</v>
+        <v>17.8</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>54.12259619622444</v>
+        <v>51.94672572350459</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>11.19472346604441</v>
+        <v>4.579314553235909</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.106854266184539</v>
+        <v>2.038211037459534</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.2093845027933772</v>
+        <v>0.2945727899367113</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6241</v>
+        <v>6441</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>鑫永洋</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>465.2246550354751</v>
+        <v>560.4207383764063</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>15.45</v>
+        <v>24.9</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>46.34756952183625</v>
+        <v>58.30571126287262</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>11.48368400061375</v>
+        <v>18.74010102092097</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.9118758669782656</v>
+        <v>0.6981145641153743</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.0664157595863397</v>
+        <v>0.0720673136884193</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6194</v>
+        <v>6239</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>459.9384265565117</v>
+        <v>558.5424807272306</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>30.55</v>
+        <v>287</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>65.91197426763512</v>
+        <v>54.98722876161556</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>18.56444066747071</v>
+        <v>9.775126547825019</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.673922534946038</v>
+        <v>0.4082512880279297</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.0876780506349264</v>
+        <v>1.538349749933881</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6239</v>
+        <v>6236</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>453.5424807272306</v>
+        <v>527.6100136986141</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>287</v>
+        <v>17.85</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>54.98722874676594</v>
+        <v>62.34111175872214</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>9.775126474200205</v>
+        <v>10.72802222258614</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.4082512880279297</v>
+        <v>0.6470188605997865</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1.538349750410908</v>
+        <v>1.982367022323533</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6210</v>
+        <v>6472</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>447.2628631187322</v>
+        <v>525.9710232663093</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>17.8</v>
+        <v>421.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.94672608333983</v>
+        <v>50.27569151227858</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>4.579316097493241</v>
+        <v>21.47895950619678</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2.038211037459534</v>
+        <v>0.7738837136404555</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.2945727866264258</v>
+        <v>1.263825371686212</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6190</v>
+        <v>6435</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>439.6646192834892</v>
+        <v>518.6420652514626</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>68.59999999999999</v>
+        <v>253.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>50.77775416105227</v>
+        <v>52.79101167371908</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>12.77166138280207</v>
+        <v>8.098720366736252</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.4768365100193492</v>
+        <v>0.8373601809609074</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.1963630308250716</v>
+        <v>2.192723398495564</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6206</v>
+        <v>6266</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>433.036910584006</v>
+        <v>505.448080021483</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>139</v>
+        <v>24.9</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>50.69751593895003</v>
+        <v>49.58365134875887</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>14.93495366503283</v>
+        <v>8.538427455836214</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3883922134014348</v>
+        <v>0.6902568812034882</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1803094857363903</v>
+        <v>0.0105393242108474</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6187</v>
+        <v>6285</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>425.3982389625526</v>
+        <v>498.9103822709467</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>1195</v>
+        <v>238</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,49 +2831,49 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>44.71636054424191</v>
+        <v>52.99368815352221</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>13.72835706701207</v>
+        <v>19.19277041623442</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.4916050500937455</v>
+        <v>1.45478122683924</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M45" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-17.41231303204849</v>
+        <v>1.114227388121178</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6441</v>
+        <v>6233</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>420.4207383764064</v>
+        <v>482.0695743483041</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>24.9</v>
+        <v>21.35</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>58.30571126561561</v>
+        <v>55.02064737640581</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>18.74010104360405</v>
+        <v>16.79100260769782</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.6981145641153743</v>
+        <v>0.6755558163131483</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0720673136598025</v>
+        <v>0.1614099976816804</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6417</v>
+        <v>6418</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>419.0415423013458</v>
+        <v>481.5757285346891</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>102</v>
+        <v>34.55</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>39.45290061509799</v>
+        <v>51.76270051188474</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>38.50243117132783</v>
+        <v>29.62341744129527</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.302163926499033</v>
+        <v>0.1094152202160514</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.197641820087207</v>
+        <v>-0.1191691632795219</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6265</v>
+        <v>6432</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>418.1219098785853</v>
+        <v>472.7582762391174</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>48.45</v>
+        <v>60.4</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>40.50182742164553</v>
+        <v>49.27311121747557</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>20.12072857768426</v>
+        <v>20.97058091625856</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4322829297482632</v>
+        <v>0.5711946558878058</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.4756110686181425</v>
+        <v>1.082007190358317</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6189</v>
+        <v>6414</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>415.7245478107495</v>
+        <v>470.7072010556364</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>49.2</v>
+        <v>374</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,49 +3043,49 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>60.44000170734354</v>
+        <v>42.32645203887837</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>13.67839985857502</v>
+        <v>23.50530754835012</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.7238251276090925</v>
+        <v>0.6067454909135692</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.2826127599641223</v>
+        <v>1.321266692489797</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6188</v>
+        <v>6234</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>408.3472694522595</v>
+        <v>465.4414877189968</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>62</v>
+        <v>37.85</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>33.41576819217651</v>
+        <v>54.230999058813</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>30.41685896672531</v>
+        <v>20.29680733431054</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.506398935503666</v>
+        <v>0.9868653522617546</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>1</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0502098099143266</v>
+        <v>0.5286082147826853</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6435</v>
+        <v>6243</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>403.6420652514626</v>
+        <v>465.3026365477501</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>253.5</v>
+        <v>39.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>52.79101167627702</v>
+        <v>49.27003396441372</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>8.098720316850347</v>
+        <v>20.17410291807317</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.8373601809609074</v>
+        <v>3.601378587819686</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>2.192723398285708</v>
+        <v>0.4794189436569769</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6279</v>
+        <v>6241</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>389.8939760574495</v>
+        <v>465.2246550354751</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>112.5</v>
+        <v>15.45</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>38.37864969150253</v>
+        <v>46.34756951096985</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>35.19637835658042</v>
+        <v>11.48368397024404</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4544712570610476</v>
+        <v>0.9118758669782656</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.0510056586681164</v>
+        <v>-0.0664157595723224</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6470</v>
+        <v>6194</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>389.2708508737744</v>
+        <v>459.9384265565117</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>43</v>
+        <v>30.55</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>52.14845653056445</v>
+        <v>65.91197423665392</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>23.62827744219377</v>
+        <v>18.56444067692023</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3275550635124111</v>
+        <v>1.673922534946038</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.1311472419608193</v>
+        <v>0.0876780506540069</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6174</v>
+        <v>6244</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>385.9387305113407</v>
+        <v>442.2937938269147</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>44.95</v>
+        <v>23.55</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>53.04440237743914</v>
+        <v>50.72279301066639</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>13.75830596253668</v>
+        <v>16.15653066207243</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.9214822437430756</v>
+        <v>1.680767911299174</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.2859364521669645</v>
+        <v>0.1864583540860164</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6229</v>
+        <v>6190</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>374.8876730004434</v>
+        <v>439.6646192834893</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>23.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>51.02435909605171</v>
+        <v>50.77775427177215</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>10.51247247384083</v>
+        <v>12.77166142359949</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.787894507393719</v>
+        <v>0.4768365100193492</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0464932613536958</v>
+        <v>0.1963630310635716</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6202</v>
+        <v>6187</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>373.0894125227732</v>
+        <v>425.4533339751006</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>58.2</v>
+        <v>1195</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>53.00848185094776</v>
+        <v>44.71636053240834</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>11.78606040428078</v>
+        <v>13.72835704790159</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.816426638421937</v>
+        <v>0.5022947219055958</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.375727851734719</v>
+        <v>-17.41231303223928</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6233</v>
+        <v>6206</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>367.0695743483041</v>
+        <v>423.036910584006</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>21.35</v>
+        <v>139</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>55.02064739514562</v>
+        <v>50.69751580643432</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>16.79100262681165</v>
+        <v>14.93495377737909</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.6755558163131483</v>
+        <v>0.3883922134014348</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.1614099976721388</v>
+        <v>0.1803094864995612</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6246</v>
+        <v>6417</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>362.5894406864217</v>
+        <v>419.0415423013457</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>12.8</v>
+        <v>102</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>49.89878720968083</v>
+        <v>39.45290056819324</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>29.50973015880708</v>
+        <v>38.50243126639941</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.1892592263872863</v>
+        <v>1.302163926499033</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0291312051984911</v>
+        <v>0.1976418202016896</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3548,21 +3548,21 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6183</v>
+        <v>6265</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>361.439450358852</v>
+        <v>418.1219098785853</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>91.3</v>
+        <v>48.45</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>46.28129600000148</v>
+        <v>40.50182742669804</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>12.93819742613824</v>
+        <v>20.12072849354107</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.8358651483913635</v>
+        <v>0.4322829297482632</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0415195026705173</v>
+        <v>-0.4756110686105068</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6263</v>
+        <v>6188</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>357.4687951312504</v>
+        <v>408.3472694522603</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>157</v>
+        <v>62</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45.40923638296545</v>
+        <v>33.4157683350104</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>15.99940255780408</v>
+        <v>30.41685889535179</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.3345619315422479</v>
+        <v>0.506398935503666</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.4189921740476858</v>
+        <v>0.0502098099906191</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6414</v>
+        <v>6237</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>355.7072010556363</v>
+        <v>404.2211869716203</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>374</v>
+        <v>37</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>42.32645206891731</v>
+        <v>62.30641641229285</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>23.50530752698596</v>
+        <v>16.87008102590127</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.6067454909135692</v>
+        <v>7.103814350115726</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>1.321266692394422</v>
+        <v>0.4112636293832947</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, rsi_strong, market_above_ma60, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6165</v>
+        <v>6279</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>355.0194527158492</v>
+        <v>389.8939760574494</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>48.95</v>
+        <v>112.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>51.65522496544414</v>
+        <v>38.3786495934306</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>14.35776239745888</v>
+        <v>35.19637842361337</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.3204236180844755</v>
+        <v>0.4544712570610476</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.1226179568863905</v>
+        <v>-0.0510056582865265</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6243</v>
+        <v>6470</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>345.3026365477501</v>
+        <v>389.2708508737744</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>39.5</v>
+        <v>43</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>49.27003397946686</v>
+        <v>52.14845627375989</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>20.17410279742279</v>
+        <v>23.62827745762274</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>3.601378587819686</v>
+        <v>0.3275550635124111</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.4794189436569769</v>
+        <v>0.1311472422851695</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6175</v>
+        <v>6217</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>344.6205923617439</v>
+        <v>387.640305997797</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>69.7</v>
+        <v>170</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>41.51972471475454</v>
+        <v>49.36629717140195</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>17.27755576882369</v>
+        <v>13.30479063962005</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.4388308517117974</v>
+        <v>0.2828585845508812</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>1</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.4208327069832864</v>
+        <v>-0.2515590357549234</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6464</v>
+        <v>6174</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>341.6280124931553</v>
+        <v>385.9387305113407</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>77</v>
+        <v>44.95</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>45.311548594078</v>
+        <v>53.04440237537673</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>21.17974311134362</v>
+        <v>13.75830597246228</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.0258545151225515</v>
+        <v>0.9214822437430756</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0017758928268377</v>
+        <v>0.2859364521955773</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6167</v>
+        <v>6261</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>330.3945452084353</v>
+        <v>375.86487855998</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>10.35</v>
+        <v>78.3</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>49.22656229574756</v>
+        <v>49.52662480919999</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>11.16743398532468</v>
+        <v>13.22340727407215</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.9258614980445508</v>
+        <v>0.7822159383367108</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0407918423388177</v>
+        <v>0.3924543909837721</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6405</v>
+        <v>6165</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>328.3159040054463</v>
+        <v>375.0194527158492</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>41.45</v>
+        <v>48.95</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>54.43748637281087</v>
+        <v>51.65522475500319</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>22.19787632557716</v>
+        <v>14.35776240588586</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.7982058273106563</v>
+        <v>0.3204236180844755</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.4999337155464521</v>
+        <v>0.1226179573443029</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6236</v>
+        <v>6229</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>327.6100136986141</v>
+        <v>374.887673000443</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>17.85</v>
+        <v>23.7</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>62.34111175872214</v>
+        <v>51.02435900770365</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10.72802222022578</v>
+        <v>10.51247241194734</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.6470188605997865</v>
+        <v>1.787894507393719</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>1.982367022323533</v>
+        <v>0.0464932614013949</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6244</v>
+        <v>6246</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>327.2937938269147</v>
+        <v>362.5894406864214</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>23.55</v>
+        <v>12.8</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>50.72279302877978</v>
+        <v>49.89878723566674</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>16.15653073065549</v>
+        <v>29.50973018677561</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.680767911299174</v>
+        <v>0.1892592263872863</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.1864583540383205</v>
+        <v>0.0291312052080315</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6451</v>
+        <v>6183</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>326.7347828857845</v>
+        <v>361.439450358852</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>412</v>
+        <v>91.3</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>45.15748999420334</v>
+        <v>46.28129598856892</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>8.165077404986041</v>
+        <v>12.93819738776076</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.2402832464634738</v>
+        <v>0.8358651483913635</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-1.136527824128973</v>
+        <v>-0.0415195026323594</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6234</v>
+        <v>6263</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>325.441487718997</v>
+        <v>357.4687951312504</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>37.85</v>
+        <v>157</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>54.2309990482064</v>
+        <v>45.40923636903661</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>20.29680721957198</v>
+        <v>15.9994025866516</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.9868653522617546</v>
+        <v>0.3345619315422479</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.5286082142579971</v>
+        <v>-0.4189921739522789</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6281</v>
+        <v>6175</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>322.3023664125237</v>
+        <v>344.6205923617439</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>51</v>
+        <v>69.7</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>43.19196891397021</v>
+        <v>41.51972472922288</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>9.444724935250274</v>
+        <v>17.27755574034018</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.246051462242154</v>
+        <v>0.4388308517117974</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.0266107557997581</v>
+        <v>0.4208327070214537</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6170</v>
+        <v>6464</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>317.7149733908975</v>
+        <v>341.6280124931552</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>48.4</v>
+        <v>77</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>55.05746488016431</v>
+        <v>45.311548594078</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.63255880133232</v>
+        <v>21.17974308230895</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.7633969650774827</v>
+        <v>0.0258545151225515</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.012523258066414</v>
+        <v>0.0017758928077551</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6259</v>
+        <v>6198</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>316.9186290747091</v>
+        <v>336.4797730940198</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>29.15</v>
+        <v>19.4</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>47.24901168968077</v>
+        <v>52.94284093054748</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>9.331955250626136</v>
+        <v>8.391078854134728</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.1999522804176186</v>
+        <v>0.5176056641686142</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.1516932617471688</v>
+        <v>0.725248758542131</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6269</v>
+        <v>6167</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>310.0840289244618</v>
+        <v>330.3945452084353</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>64.8</v>
+        <v>10.35</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>48.5122088792365</v>
+        <v>49.22656191718546</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.07883713687446</v>
+        <v>11.16743397721342</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.2668226654170578</v>
+        <v>0.9258614980445508</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.4559629281492069</v>
+        <v>0.0407918424859618</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6432</v>
+        <v>6269</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>302.7582762391174</v>
+        <v>330.0840289244618</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>60.4</v>
+        <v>64.8</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>49.27311122797026</v>
+        <v>48.51220901062901</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>20.97058089910592</v>
+        <v>13.07883764282984</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.5711946558878058</v>
+        <v>0.2668226654170578</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>1.082007190291535</v>
+        <v>-0.4559629286643467</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6235</v>
+        <v>6405</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>296.7034726959216</v>
+        <v>328.3159040054463</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>38.7</v>
+        <v>41.45</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>50.49085084781112</v>
+        <v>54.43748636460417</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>12.55513205894832</v>
+        <v>22.19787643486348</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.62343459484132</v>
+        <v>0.7982058273106563</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.1213603337784844</v>
+        <v>0.4999337155178392</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6277</v>
+        <v>6451</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>293.1407128457347</v>
+        <v>326.7347828857845</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>77.8</v>
+        <v>412</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>47.33372235108264</v>
+        <v>45.15748999570672</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>17.10191091425062</v>
+        <v>8.165077412666923</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.4130871344689618</v>
+        <v>0.2402832464634738</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.0036963860596314</v>
+        <v>-1.136527824415174</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6191</v>
+        <v>6281</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>288.4548226217462</v>
+        <v>322.3023664125197</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>82.3</v>
+        <v>51</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>45.75095631935758</v>
+        <v>43.1919690206711</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>13.94461226373439</v>
+        <v>9.444724956286535</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.6403460571916633</v>
+        <v>1.246051462242154</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.2965934580430136</v>
+        <v>-0.0266107558188365</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6449</v>
+        <v>6446</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>283.8633905955883</v>
+        <v>321.8016867489027</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>209.5</v>
+        <v>1155</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>41.62341362083963</v>
+        <v>37.70268301805562</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>12.15538146287669</v>
+        <v>19.91332230406956</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.332508490117131</v>
+        <v>0.3363047400516636</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0108765475589116</v>
+        <v>-17.23431402616788</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6215</v>
+        <v>6442</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>280.3097969186821</v>
+        <v>319.4928674430854</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>96.8</v>
+        <v>1530</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>46.0971153320138</v>
+        <v>46.36378420449738</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>10.92089902864576</v>
+        <v>14.53493402150338</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.641946204768259</v>
+        <v>0.335084557587092</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0199639995715463</v>
+        <v>-23.03758894280538</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6230</v>
+        <v>6170</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>279.7222835757408</v>
+        <v>317.7149733908975</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>113</v>
+        <v>48.4</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>53.77027255238332</v>
+        <v>55.05746522428631</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>13.87008615331944</v>
+        <v>15.63255877127347</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.6258834396525222</v>
+        <v>0.7633969650774827</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.4863430400013534</v>
+        <v>-0.0125232581045694</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6415</v>
+        <v>6259</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>276.3991153106608</v>
+        <v>316.9186290747091</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>425.5</v>
+        <v>29.15</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>48.46548198291947</v>
+        <v>47.24901167068825</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>9.678042243746511</v>
+        <v>9.331955158453816</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4839489536893613</v>
+        <v>0.1999522804176186</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>3.296308894797207</v>
+        <v>0.1516932618139457</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6217</v>
+        <v>6272</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>272.640305997797</v>
+        <v>301.1287513341082</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>170</v>
+        <v>25.3</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>49.36629717671546</v>
+        <v>42.92351265023769</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>13.30479055911774</v>
+        <v>29.63784018824169</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.2828585845508812</v>
+        <v>0.3033643822283974</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.2515590358789319</v>
+        <v>-0.3388584251234423</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6177</v>
+        <v>6277</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>272.3237921966169</v>
+        <v>293.1407128457347</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>46.2</v>
+        <v>77.8</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>41.60083964348086</v>
+        <v>47.33372237938669</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>17.57008109226898</v>
+        <v>17.10191097450986</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.7003234123180839</v>
+        <v>0.4130871344689618</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.1415884161269601</v>
+        <v>-0.0036963860596314</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6285</v>
+        <v>6191</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>268.9103822709466</v>
+        <v>288.4548226217462</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>238</v>
+        <v>82.3</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>52.99368825142734</v>
+        <v>45.75095614132883</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>19.19277029722027</v>
+        <v>13.94461242522091</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.45478122683924</v>
+        <v>0.6403460571916633</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>1.114227386594811</v>
+        <v>0.2965934580430136</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6185</v>
+        <v>6235</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>263.5818722190636</v>
+        <v>286.7034726959216</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>12.45</v>
+        <v>38.7</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>38.90267519090451</v>
+        <v>50.49085098261284</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>25.06707430700602</v>
+        <v>12.55513202160818</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.5733843133584536</v>
+        <v>1.62343459484132</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0360409964623214</v>
+        <v>0.1213603339883574</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6261</v>
+        <v>6449</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>260.86487855998</v>
+        <v>283.8633905955883</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>78.3</v>
+        <v>209.5</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>49.52662479435693</v>
+        <v>41.62341350278633</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>13.22340730760904</v>
+        <v>12.15538149636485</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.7822159383367108</v>
+        <v>0.332508490117131</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.392454390926528</v>
+        <v>-0.0108765455555888</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6163</v>
+        <v>6215</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>260.4610578039624</v>
+        <v>280.3097969186821</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>41.4</v>
+        <v>96.8</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>49.91367466323965</v>
+        <v>46.09711529734605</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>11.00547865775146</v>
+        <v>10.92089896110866</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.2360394854377</v>
+        <v>0.641946204768259</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.197374039939337</v>
+        <v>0.0199639995715463</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6412</v>
+        <v>6230</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>248.4185516522064</v>
+        <v>279.722283575741</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>113</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>37.79188030691747</v>
+        <v>53.77027259367529</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>26.03791617625213</v>
+        <v>13.87008615017612</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5826557882460266</v>
+        <v>0.6258834396525222</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.1685064754117808</v>
+        <v>0.4863430399059389</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6446</v>
+        <v>6177</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>246.8016867489027</v>
+        <v>272.3237921966168</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>1155</v>
+        <v>46.2</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>37.70268301546445</v>
+        <v>41.60083965360595</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>19.9133222574413</v>
+        <v>17.57008105511164</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.3363047400516636</v>
+        <v>0.7003234123180839</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-17.23431402626345</v>
+        <v>-0.1415884160124819</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6192</v>
+        <v>6415</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>241.7573065478442</v>
+        <v>266.3991153106608</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>110.5</v>
+        <v>425.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,49 +5322,49 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>38.96564999104772</v>
+        <v>48.46548197816509</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>27.41533883632093</v>
+        <v>9.678042294048854</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4247648389105568</v>
+        <v>0.4839489536893613</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.1428655265834959</v>
+        <v>3.29630889517877</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6220</v>
+        <v>6185</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>239.0563385192111</v>
+        <v>263.5818722190636</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>25.25</v>
+        <v>12.45</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>40.3464155244155</v>
+        <v>38.90267581408174</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>10.5649980644042</v>
+        <v>25.0670743646054</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3521453903540544</v>
+        <v>0.5733843133584536</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>2</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0611514874326393</v>
+        <v>0.0360409965195589</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6223</v>
+        <v>6163</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>238.3441852836885</v>
+        <v>260.4610578039624</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>5415</v>
+        <v>41.4</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>47.34251385603016</v>
+        <v>49.91367464634831</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>12.00169648706659</v>
+        <v>11.00547870468412</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5303222279471514</v>
+        <v>1.2360394854377</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>14.58219559583253</v>
+        <v>0.1973740399775023</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6237</v>
+        <v>6412</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>234.2211869716199</v>
+        <v>248.4185516522064</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>37</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>62.30641647500937</v>
+        <v>37.79188060992104</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>16.87008108269483</v>
+        <v>26.03791619167086</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>7.103814350115726</v>
+        <v>0.5826557882460266</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.4112636291543399</v>
+        <v>0.1685064753163809</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6474</v>
+        <v>6192</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>228.0903613714612</v>
+        <v>241.7573065478441</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>35.55</v>
+        <v>110.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>39.89543642749751</v>
+        <v>38.96565003426014</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>15.17051902652435</v>
+        <v>27.41533882070444</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.6861138362604273</v>
+        <v>0.4247648389105568</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0039333713531289</v>
+        <v>-0.1428655266598013</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6184</v>
+        <v>6220</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>227.7043836813466</v>
+        <v>239.0563385192111</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>40.3</v>
+        <v>25.25</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>44.30780705623803</v>
+        <v>40.34641565356581</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>36.43845464541895</v>
+        <v>10.5649980482419</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.230954563436029</v>
+        <v>0.3521453903540544</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.1371158929345433</v>
+        <v>0.0611514874421841</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6409</v>
+        <v>6223</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>217.8255547095972</v>
+        <v>238.3441852836849</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>879</v>
+        <v>5415</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>37.98699352719899</v>
+        <v>47.3425138522506</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>18.80190177282774</v>
+        <v>12.0016963799206</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.6084751477765469</v>
+        <v>0.5303222279471514</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-1.979010491320892</v>
+        <v>14.58219559201653</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6465</v>
+        <v>6474</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>215.2652422590988</v>
+        <v>228.0903613714612</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>41.65</v>
+        <v>35.55</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>34.42493306237198</v>
+        <v>39.89543620445682</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>13.30479036477028</v>
+        <v>15.17051908727227</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.514791135031893</v>
+        <v>0.6861138362604273</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0520320577513255</v>
+        <v>-0.0039333712672736</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6282</v>
+        <v>6184</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>208.9388482070136</v>
+        <v>227.7043836813466</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>42.85</v>
+        <v>40.3</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>42.02876393445669</v>
+        <v>44.30780707882468</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>17.0078469766511</v>
+        <v>36.43845471916114</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.5752956218348082</v>
+        <v>0.230954563436029</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.1880660906413696</v>
+        <v>0.1371158929345433</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6208</v>
+        <v>6409</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>206.3717116009259</v>
+        <v>217.8255547095977</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>74.3</v>
+        <v>879</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>40.5825287827156</v>
+        <v>37.98699343872535</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>15.19398292998323</v>
+        <v>18.80190184560387</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.283038536190505</v>
+        <v>0.6084751477765469</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.2108127003181672</v>
+        <v>-1.979010483689155</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6419</v>
+        <v>6465</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>205.9716635143944</v>
+        <v>215.2652422590988</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>149</v>
+        <v>41.65</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>47.59814510762627</v>
+        <v>34.42493330510166</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>9.791830198362939</v>
+        <v>13.30479039063131</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.2029733890584552</v>
+        <v>0.514791135031893</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.4540312675642637</v>
+        <v>0.0520320577022783</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5880,21 +5880,21 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6442</v>
+        <v>6282</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>199.4928674430853</v>
+        <v>208.9388482070138</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>1530</v>
+        <v>42.85</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>46.36378422265413</v>
+        <v>42.02876394873476</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>14.53493406765675</v>
+        <v>17.00784704889255</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.335084557587092</v>
+        <v>0.5752956218348082</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-23.03758894299614</v>
+        <v>0.1880660907081617</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6272</v>
+        <v>6208</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>191.1287513341082</v>
+        <v>206.3717116009259</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>25.3</v>
+        <v>74.3</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>42.92351268013637</v>
+        <v>40.58252876442935</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>29.63784018868303</v>
+        <v>15.19398287885846</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3033643822283974</v>
+        <v>0.283038536190505</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.3388584251425245</v>
+        <v>0.2108127003754232</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6216</v>
+        <v>6419</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>186.5728803333345</v>
+        <v>205.9716635143944</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>19.55</v>
+        <v>149</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>32.64488451974105</v>
+        <v>47.59814510762627</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>44.79973581092147</v>
+        <v>9.79183020897079</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.2236491775487307</v>
+        <v>0.2029733890584552</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0402282386823682</v>
+        <v>-0.454031267487917</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6284</v>
+        <v>6283</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>182.7786128165065</v>
+        <v>192.2737447752444</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>74.3</v>
+        <v>18.85</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>42.57860506545421</v>
+        <v>41.12935780239491</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>7.104446523331147</v>
+        <v>21.7592091179905</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.406630448438915</v>
+        <v>0.2721286845972557</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.09112805039791121</v>
+        <v>0.0308807551060936</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6222</v>
+        <v>6216</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>179.6655489594883</v>
+        <v>186.5728803333345</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>18.4</v>
+        <v>19.55</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>46.75410528405131</v>
+        <v>32.64488462725652</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>4.383104779008875</v>
+        <v>44.79973580647071</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.3316587358170433</v>
+        <v>0.2236491775487307</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.1362827542321408</v>
+        <v>0.0402282386728288</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6462</v>
+        <v>6284</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>176.8008097181372</v>
+        <v>182.7786128165065</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>99.7</v>
+        <v>74.3</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,49 +6170,49 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>51.54621108585258</v>
+        <v>42.57860504141423</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>11.73818708155002</v>
+        <v>7.104446560858931</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.5492099394842883</v>
+        <v>0.406630448438915</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.2014240429350475</v>
+        <v>-0.0911280502261935</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6161</v>
+        <v>6222</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>捷波</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>155.804205017652</v>
+        <v>179.6655489594881</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>49.15</v>
+        <v>18.4</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>47.12795399786205</v>
+        <v>46.75410530755013</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>10.83835686252582</v>
+        <v>4.383104840893759</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.4022046388043475</v>
+        <v>0.3316587358170433</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0637214177519853</v>
+        <v>-0.136282754270298</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6411</v>
+        <v>6462</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>147.8897659861489</v>
+        <v>176.8008097181369</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,25 +6276,25 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>46.81199556690092</v>
+        <v>51.54621104753953</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>8.653018630678815</v>
+        <v>11.73818705462402</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.3360373873426625</v>
+        <v>0.5492099394842883</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.1512677816430648</v>
+        <v>0.2014240423626525</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6304,21 +6304,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6176</v>
+        <v>6161</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>捷波</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>139.5218620707787</v>
+        <v>155.804205017652</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>91.8</v>
+        <v>49.15</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>50.63805034766321</v>
+        <v>47.12795400677779</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>18.01217959638966</v>
+        <v>10.8383568755214</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.515510380048391</v>
+        <v>0.4022046388043475</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0794412766489327</v>
+        <v>0.0637214177042897</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6198</v>
+        <v>6411</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>136.4797730940198</v>
+        <v>147.8897659861489</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>19.4</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>52.94284093054748</v>
+        <v>46.81199547501882</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>8.391079001643146</v>
+        <v>8.653018608308923</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5176056641686142</v>
+        <v>0.3360373873426625</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.725248758542131</v>
+        <v>0.1512677818147805</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6203</v>
+        <v>6176</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>126.8471884399789</v>
+        <v>139.5218620707787</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>59.6</v>
+        <v>91.8</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>42.06665101121022</v>
+        <v>50.63805034766321</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>7.749668557607208</v>
+        <v>18.01217968197022</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.4309727197575089</v>
+        <v>0.515510380048391</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.1108212975526302</v>
+        <v>-0.0794412769759196</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6276</v>
+        <v>6203</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>海韻電</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>83.99633184679176</v>
+        <v>126.8471884399789</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>19.65</v>
+        <v>59.6</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>46.72785907180651</v>
+        <v>42.06665102820589</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>15.56384339514588</v>
+        <v>7.749668534210134</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.242251007067564</v>
+        <v>0.4309727197575089</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0022391159293984</v>
+        <v>0.1108212976098693</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6283</v>
+        <v>6276</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>77.27374477524437</v>
+        <v>83.9963318467918</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>18.85</v>
+        <v>19.65</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>41.12935780239491</v>
+        <v>46.72785904238908</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>21.75920914638763</v>
+        <v>15.56384328870683</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.2721286845972557</v>
+        <v>1.242251007067564</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,11 +6559,11 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0308807551156317</v>
+        <v>-0.0022391157767619</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>

--- a/output/full_scan/batch_seq6_2026-09-24.xlsx
+++ b/output/full_scan/batch_seq6_2026-09-24.xlsx
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>66.66258263654424</v>
+        <v>66.66258264529621</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>20.03638227562102</v>
+        <v>20.03638233254001</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.008072549259758</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0279659061983181</v>
+        <v>0.0279659058479957</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>64.83174482953652</v>
+        <v>64.83174483637885</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>21.4997740037675</v>
+        <v>21.49977401398439</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>8.443961698534848</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1.015667107052638</v>
+        <v>1.015667107145368</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>71.18692325866445</v>
+        <v>71.18692326537445</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>20.36263272905853</v>
+        <v>20.36263273942881</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>2.24580486811646</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>63.0666188986628</v>
+        <v>63.06661889711793</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14.68035603350259</v>
+        <v>14.68035599422468</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1.897767706804681</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.320441410873102</v>
+        <v>1.320441410945215</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>940.6269194686164</v>
+        <v>940.6269194686192</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>565</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>65.54270116081905</v>
+        <v>65.54270119928063</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>15.66891953482067</v>
+        <v>15.66891963656409</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0.9584558643329044</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>4.653624494291645</v>
+        <v>4.653624493261205</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>68.11406770902241</v>
+        <v>68.11406773988737</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>43.05596085311367</v>
+        <v>43.05596087803512</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1.350681376804406</v>
@@ -856,7 +856,7 @@
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>882.0855854405762</v>
+        <v>882.0855854405756</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1495</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>56.400107946741</v>
+        <v>56.40010796069737</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>19.34389631197316</v>
+        <v>19.34389638874685</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>1.349263704100556</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>12.90742260449349</v>
+        <v>12.90742260212381</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>58.26573932016866</v>
+        <v>58.26573933002864</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>15.61506634594098</v>
+        <v>15.61506640517012</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>1.74736065382166</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.446095108044223</v>
+        <v>1.446095107941201</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>856.3184997482543</v>
+        <v>856.3184997482542</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>132</v>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>63.59559106136845</v>
+        <v>63.59559110336602</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>22.17453390448567</v>
+        <v>22.17453390881341</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>1.069878972973927</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>2.69445116942654</v>
+        <v>2.69445116932351</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>57.91764608773407</v>
+        <v>57.91764609460841</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>24.12880708304367</v>
+        <v>24.12880710767694</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>0.3509783905401061</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.249979062613372</v>
+        <v>-0.2499790627163989</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>64.3875813106133</v>
+        <v>64.38758131685535</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>20.97541043626613</v>
+        <v>20.97541043588995</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0.9196191487819916</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>3.835269044018928</v>
+        <v>3.835269043957112</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>56.07705364981348</v>
+        <v>56.07705361907149</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>28.24656522959186</v>
+        <v>28.24656523779491</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0.409165748070089</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.4303852299350659</v>
+        <v>0.4303852295229902</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>43.5123613101049</v>
+        <v>43.51236130359737</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>30.01213485923392</v>
+        <v>30.0121348228333</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>10.36975850628528</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-3.156081681665603</v>
+        <v>-3.156081681531665</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>62.65092002827535</v>
+        <v>62.65092003189135</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>30.71079744674877</v>
+        <v>30.71079743514897</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0.2359423414332075</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.2252700331006494</v>
+        <v>0.2252700332861126</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>73.21134644791351</v>
+        <v>73.21134643791333</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46.69088127013588</v>
+        <v>46.69088128627345</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>1.2929223485303</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>5.39644513611394</v>
+        <v>5.396445136484807</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>52.12986569519275</v>
+        <v>52.12986570728569</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>42.62926850747657</v>
+        <v>42.62926852689309</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>0.3708707727099934</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-1.198090568126521</v>
+        <v>-1.198090568105901</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>62.63390265223265</v>
+        <v>62.63390267570716</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>23.28980005677465</v>
+        <v>23.28980001977224</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>2.259934107518183</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.6575100139948079</v>
+        <v>0.6575100139226868</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>723.1294712635267</v>
+        <v>723.1294712635266</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>107.5</v>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>64.36927852414901</v>
+        <v>64.36927851827079</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>23.51868146081346</v>
+        <v>23.5186814405634</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>1.218678252716549</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1.361157774871322</v>
+        <v>1.361157775118588</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>59.6111060781836</v>
+        <v>59.61110604525277</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>29.83339524561203</v>
+        <v>29.83339506359597</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>0.5071471822056217</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.0336552233637077</v>
+        <v>-0.0336552234152223</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>56.17758028652718</v>
+        <v>56.17758027949982</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>15.41856729698002</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>2.053150232184326</v>
+        <v>2.05315023241099</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>685.7153359639725</v>
+        <v>685.7153359639732</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>85.7</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>55.81718956452371</v>
+        <v>55.81718957299701</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>20.4142183625333</v>
+        <v>20.4142183801418</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>0.4982216913324923</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.4346386187129494</v>
+        <v>0.4346386188365926</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>63.79576574570996</v>
+        <v>63.79576576256471</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>18.39934887542577</v>
+        <v>18.39934889740825</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>1.430031148977345</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.789170172527805</v>
+        <v>1.789170172630829</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>683.9215222616863</v>
+        <v>683.9215222616861</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>157.5</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>62.08560633698952</v>
+        <v>62.08560634492002</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>18.47983130568164</v>
+        <v>18.47983131370662</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>2.269757034895909</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.6086841702846781</v>
+        <v>0.6086841704907591</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>63.50779681701987</v>
+        <v>63.50779682507245</v>
       </c>
       <c r="I25" s="2" t="n">
         <v>37.54616092363761</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.1797555502959937</v>
+        <v>-0.1797555503680925</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>64.06823281893976</v>
+        <v>64.06823286879842</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>30.43473403683808</v>
+        <v>30.43473402607072</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>0.5644020238586532</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.439548690416242</v>
+        <v>1.439548690457456</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>61.49437370620001</v>
+        <v>61.4943737089535</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>18.51541259867267</v>
+        <v>18.51541266220724</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>0.6017233650445784</v>
@@ -1916,7 +1916,7 @@
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>664.5775541717605</v>
+        <v>664.5775541717601</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>274</v>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>58.42997935578455</v>
+        <v>58.42997937481366</v>
       </c>
       <c r="I28" s="2" t="n">
         <v>28.20794361189195</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.5430680892161792</v>
+        <v>0.5430680888041124</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>53.58585285735273</v>
+        <v>53.5858527257891</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>27.55824196537597</v>
+        <v>27.5582420087473</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>0.3158218194710098</v>
@@ -2075,7 +2075,7 @@
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>640.72454781075</v>
+        <v>640.7245478107499</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>49.2</v>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>60.44000170734354</v>
+        <v>60.44000185171889</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>13.67839986329985</v>
+        <v>13.6783998427762</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>0.7238251276090925</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.2826127597924111</v>
+        <v>0.28261275960696</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>626.7572886142935</v>
+        <v>626.757288614293</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>320</v>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>57.56544904277526</v>
+        <v>57.56544905015739</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>14.23362223683571</v>
+        <v>14.23362223805619</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.5544628058873015</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>2.284717295549552</v>
+        <v>2.284717295858622</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>53.00848179598765</v>
+        <v>53.00848187069934</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>11.78606048173884</v>
+        <v>11.7860605299908</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0.816426638421937</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.3757278517633402</v>
+        <v>0.3757278515469836</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>46.24721673166113</v>
+        <v>46.24721718938914</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>26.99637978708038</v>
+        <v>26.99637984701481</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.5352959447436444</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0816399018393856</v>
+        <v>0.08163990101515189</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>54.12259619079699</v>
+        <v>54.12259641874993</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>11.19472339863702</v>
+        <v>11.1947234162119</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>1.106854266184539</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.2093845028315398</v>
+        <v>0.2093845028624441</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>56.29697327968442</v>
+        <v>56.29697321883355</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>20.87925687214075</v>
+        <v>20.87925688444003</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>0.8109296247975909</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.1093957968767523</v>
+        <v>0.1093957969159026</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>54.75179759228131</v>
+        <v>54.75179760268308</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>24.25431229264032</v>
+        <v>24.25431224395101</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>0.5113231867855531</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.2460884426102092</v>
+        <v>-0.2460884423938569</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>51.94672572350459</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>4.579314553235909</v>
+        <v>4.579314586071396</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>2.038211037459534</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.2945727899367113</v>
+        <v>0.2945727899264081</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>560.4207383764063</v>
+        <v>560.4207383764062</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>24.9</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>58.30571126287262</v>
+        <v>58.30571125283373</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>18.74010102092097</v>
+        <v>18.74010101154888</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.6981145641153743</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0720673136884193</v>
+        <v>0.0720673137090254</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>54.98722876161556</v>
+        <v>54.98722877227682</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>9.775126547825019</v>
+        <v>9.775126560589136</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.4082512880279297</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1.538349749933881</v>
+        <v>1.538349749727842</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>62.34111175872214</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>10.72802222258614</v>
+        <v>10.7280222251487</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.6470188605997865</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>50.27569151227858</v>
+        <v>50.27569225450445</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>21.47895950619678</v>
+        <v>21.47895961386707</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>0.7738837136404555</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1.263825371686212</v>
+        <v>1.263825345104759</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>52.79101167371908</v>
+        <v>52.79101168841078</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>8.098720366736252</v>
+        <v>8.098720347804557</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>0.8373601809609074</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>2.192723398495564</v>
+        <v>2.19272339866041</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>505.448080021483</v>
+        <v>505.4480800214831</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>24.9</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>49.58365134875887</v>
+        <v>49.58365129782495</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>8.538427455836214</v>
+        <v>8.538427430290829</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.6902568812034882</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0105393242108474</v>
+        <v>0.0105393242520599</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>52.99368815352221</v>
+        <v>52.99368818698658</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>19.19277041623442</v>
+        <v>19.19277040414516</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>1.45478122683924</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.114227388121178</v>
+        <v>1.114227387709052</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>55.02064737640581</v>
+        <v>55.02064738750971</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>16.79100260769782</v>
+        <v>16.79100262295927</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.6755558163131483</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.1614099976816804</v>
+        <v>0.1614099976713774</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>51.76270051188474</v>
+        <v>51.76270038380225</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>29.62341744129527</v>
+        <v>29.62341746619241</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.1094152202160514</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.1191691632795219</v>
+        <v>-0.1191691628571076</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>49.27311121747557</v>
+        <v>49.27311124492324</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>20.97058091625856</v>
+        <v>20.97058091938624</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.5711946558878058</v>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>42.32645203887837</v>
+        <v>42.32645212393808</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>23.50530754835012</v>
+        <v>23.5053075816047</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0.6067454909135692</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>1.321266692489797</v>
+        <v>1.321266691768631</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>465.4414877189968</v>
+        <v>465.4414877189964</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>37.85</v>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>54.230999058813</v>
+        <v>54.23099885696675</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>20.29680733431054</v>
+        <v>20.29680774230329</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>0.9868653522617546</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.5286082147826853</v>
+        <v>0.5286082154111575</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>49.27003396441372</v>
+        <v>49.27003401400765</v>
       </c>
       <c r="I51" s="2" t="n">
         <v>20.17410291807317</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.4794189436569769</v>
+        <v>0.4794189435848568</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>46.34756951096985</v>
+        <v>46.34756962799259</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>11.48368397024404</v>
+        <v>11.48368400662731</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>0.9118758669782656</v>
@@ -3241,7 +3241,7 @@
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>459.9384265565117</v>
+        <v>459.9384265565353</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>30.55</v>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>65.91197423665392</v>
+        <v>65.9119741398849</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>18.56444067692023</v>
+        <v>18.56444068287822</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>1.673922534946038</v>
@@ -3308,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>50.72279301066639</v>
+        <v>50.72279302367088</v>
       </c>
       <c r="I54" s="2" t="n">
         <v>16.15653066207243</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.1864583540860164</v>
+        <v>0.1864583541066218</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>439.6646192834893</v>
+        <v>439.6646192834889</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>68.59999999999999</v>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>50.77775427177215</v>
+        <v>50.77775406772084</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>12.77166142359949</v>
+        <v>12.77166140010748</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>0.4768365100193492</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.1963630310635716</v>
+        <v>0.1963630318774921</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>44.71636053240834</v>
+        <v>44.7163605359483</v>
       </c>
       <c r="I56" s="2" t="n">
         <v>13.72835704790159</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-17.41231303223928</v>
+        <v>-17.41231303429979</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>50.69751580643432</v>
+        <v>50.69751589878662</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>14.93495377737909</v>
+        <v>14.93495370666925</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.3883922134014348</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.1803094864995612</v>
+        <v>0.1803094858813961</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>419.0415423013457</v>
+        <v>419.0415423013458</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>102</v>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>39.45290056819324</v>
+        <v>39.4529006043575</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>38.50243126639941</v>
+        <v>38.5024312396481</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>1.302163926499033</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.1976418202016896</v>
+        <v>0.1976418200574481</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>40.50182742669804</v>
+        <v>40.50182741793139</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>20.12072849354107</v>
+        <v>20.12072849093827</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.4322829297482632</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.4756110686105068</v>
+        <v>-0.4756110685796</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>408.3472694522603</v>
+        <v>408.3472694522605</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>62</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>33.4157683350104</v>
+        <v>33.41576828373668</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>30.41685889535179</v>
+        <v>30.41685899161678</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>0.506398935503666</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0502098099906191</v>
+        <v>0.050209810382142</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>404.2211869716203</v>
+        <v>404.2211869716205</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>37</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>62.30641641229285</v>
+        <v>62.30641638438206</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>16.87008102590127</v>
+        <v>16.87008103914424</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>7.103814350115726</v>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>38.3786495934306</v>
+        <v>38.37864969904653</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>35.19637842361337</v>
+        <v>35.19637843995342</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>0.4544712570610476</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>52.14845627375989</v>
+        <v>52.14845639667488</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>23.62827745762274</v>
+        <v>23.62827750772938</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.3275550635124111</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.1311472422851695</v>
+        <v>0.1311472423572883</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>49.36629717140195</v>
+        <v>49.3662971753635</v>
       </c>
       <c r="I64" s="2" t="n">
         <v>13.30479063962005</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>53.04440237537673</v>
+        <v>53.04440237315566</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>13.75830597246228</v>
+        <v>13.75830598057892</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.9214822437430756</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.2859364521955773</v>
+        <v>0.2859364522161847</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>49.52662480919999</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>13.22340727407215</v>
+        <v>13.22340730764942</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.7822159383367108</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.3924543909837721</v>
+        <v>0.3924543911279985</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>51.65522475500319</v>
+        <v>51.65522489346169</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>14.35776240588586</v>
+        <v>14.35776235694837</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.3204236180844755</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.1226179573443029</v>
+        <v>0.1226179572618773</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>374.887673000443</v>
+        <v>374.8876730004434</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>23.7</v>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>51.02435900770365</v>
+        <v>51.02435907135261</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10.51247241194734</v>
+        <v>10.51247246019061</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>1.787894507393719</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0464932614013949</v>
+        <v>0.0464932613910926</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>49.89878723566674</v>
+        <v>49.89878730562882</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>29.50973018677561</v>
+        <v>29.50973019397893</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>0.1892592263872863</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0291312052080315</v>
+        <v>0.0291312052389402</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>46.28129598856892</v>
+        <v>46.2812960131929</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>12.93819738776076</v>
+        <v>12.93819722589178</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.8358651483913635</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.0415195026323594</v>
+        <v>-0.0415195026117587</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>45.40923636903661</v>
+        <v>45.4092363990372</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>15.9994025866516</v>
+        <v>15.9994026000481</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>0.3345619315422479</v>
@@ -4248,7 +4248,7 @@
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>344.6205923617439</v>
+        <v>344.6205923617438</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>69.7</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>41.51972472922288</v>
+        <v>41.51972473181976</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>17.27755574034018</v>
+        <v>17.27755573500607</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>0.4388308517117974</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.4208327070214537</v>
+        <v>0.4208327071244833</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45.311548594078</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>21.17974308230895</v>
+        <v>21.1797430643264</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.0258545151225515</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0017758928077551</v>
+        <v>0.0017758927871598</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>52.94284093054748</v>
+        <v>52.94284092517208</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>8.391078854134728</v>
+        <v>8.391078879284182</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0.5176056641686142</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>49.22656191718546</v>
+        <v>49.22656237582801</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>11.16743397721342</v>
+        <v>11.16743399310105</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.9258614980445508</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0407918424859618</v>
+        <v>0.040791842503621</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>48.51220901062901</v>
+        <v>48.51220891310973</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>13.07883764282984</v>
+        <v>13.07883754643277</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.2668226654170578</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.4559629286643467</v>
+        <v>-0.4559629283140562</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>54.43748636460417</v>
+        <v>54.43748638967728</v>
       </c>
       <c r="I77" s="2" t="n">
         <v>22.19787643486348</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.4999337155178392</v>
+        <v>0.4999337154560176</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>326.7347828857845</v>
+        <v>326.7347828857846</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>412</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>45.15748999570672</v>
+        <v>45.15749001467479</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>8.165077412666923</v>
+        <v>8.165077429541601</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0.2402832464634738</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-1.136527824415174</v>
+        <v>-1.136527824621186</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>322.3023664125197</v>
+        <v>322.302366412524</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>51</v>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>43.1919690206711</v>
+        <v>43.19196893741344</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>9.444724956286535</v>
+        <v>9.444725035095598</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>1.246051462242154</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0266107558188365</v>
+        <v>-0.0266107557776273</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>37.70268301805562</v>
+        <v>37.70268303386835</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>19.91332230406956</v>
+        <v>19.91332229994196</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>0.3363047400516636</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-17.23431402616788</v>
+        <v>-17.2343140257558</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>319.4928674430854</v>
+        <v>319.4928674430853</v>
       </c>
       <c r="E81" s="2" t="n">
         <v>1530</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>46.36378420449738</v>
+        <v>46.3637842240508</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>14.53493402150338</v>
+        <v>14.53493405065067</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>0.335084557587092</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-23.03758894280538</v>
+        <v>-23.03758894672034</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>55.05746522428631</v>
+        <v>55.0574647690319</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>15.63255877127347</v>
+        <v>15.63255880519765</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>0.7633969650774827</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.0125232581045694</v>
+        <v>-0.0125232577130676</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>47.24901167068825</v>
+        <v>47.24901165534814</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>9.331955158453816</v>
+        <v>9.33195505922318</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.1999522804176186</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.1516932618139457</v>
+        <v>0.1516932618448554</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>42.92351265023769</v>
+        <v>42.92351270016616</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>29.63784018824169</v>
+        <v>29.6378401882417</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0.3033643822283974</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.3388584251234423</v>
+        <v>-0.3388584251955637</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>47.33372237938669</v>
+        <v>47.33372239767546</v>
       </c>
       <c r="I85" s="2" t="n">
         <v>17.10191097450986</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0036963860596314</v>
+        <v>-0.0036963859566039</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>288.4548226217462</v>
+        <v>288.454822621746</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>82.3</v>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>45.75095614132883</v>
+        <v>45.75095641830281</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>13.94461242522091</v>
+        <v>13.94461235866969</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.6403460571916633</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.2965934580430136</v>
+        <v>0.2965934572187685</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>50.49085098261284</v>
+        <v>50.49085074411749</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>12.55513202160818</v>
+        <v>12.55513224158592</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>1.62343459484132</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.1213603339883574</v>
+        <v>0.1213603345035025</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>283.8633905955883</v>
+        <v>283.8633905955882</v>
       </c>
       <c r="E88" s="2" t="n">
         <v>209.5</v>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>41.62341350278633</v>
+        <v>41.6234135494498</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>12.15538149636485</v>
+        <v>12.15538151427203</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>0.332508490117131</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0108765455555888</v>
+        <v>-0.0108765461737343</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>280.3097969186821</v>
+        <v>280.3097969186824</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>96.8</v>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>46.09711529734605</v>
+        <v>46.09711559661935</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>10.92089896110866</v>
+        <v>10.92089896110865</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.641946204768259</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0199639995715463</v>
+        <v>0.0199639993654718</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>279.722283575741</v>
+        <v>279.7222835757408</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>113</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>53.77027259367529</v>
+        <v>53.77027263640132</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>13.87008615017612</v>
+        <v>13.87008616059449</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>0.6258834396525222</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.4863430399059389</v>
+        <v>0.4863430402150366</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>41.60083965360595</v>
+        <v>41.60083912676578</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>17.57008105511164</v>
+        <v>17.57008104591565</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>0.7003234123180839</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.1415884160124819</v>
+        <v>-0.1415884158682428</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>48.46548197816509</v>
+        <v>48.46548197560504</v>
       </c>
       <c r="I92" s="2" t="n">
         <v>9.678042294048854</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>3.29630889517877</v>
+        <v>3.296308895384819</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>38.90267581408174</v>
+        <v>38.90267472591915</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>25.0670743646054</v>
+        <v>25.06707505837024</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.5733843133584536</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0360409965195589</v>
+        <v>0.0360409968286455</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>260.4610578039624</v>
+        <v>260.4610578039632</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>41.4</v>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>49.91367464634831</v>
+        <v>49.91367467182027</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>11.00547870468412</v>
+        <v>11.00547871075513</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>1.2360394854377</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.1973740399775023</v>
+        <v>0.1973740399671954</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>37.79188060992104</v>
+        <v>37.79188046827763</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>26.03791619167086</v>
+        <v>26.03791649979354</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.5826557882460266</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.1685064753163809</v>
+        <v>0.1685064757284906</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>241.7573065478441</v>
+        <v>241.7573065478444</v>
       </c>
       <c r="E96" s="2" t="n">
         <v>110.5</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>38.96565003426014</v>
+        <v>38.96565007686494</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>27.41533882070444</v>
+        <v>27.41533883992354</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.4247648389105568</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.1428655266598013</v>
+        <v>-0.1428655265773857</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>239.0563385192111</v>
+        <v>239.0563385192113</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>25.25</v>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>40.34641565356581</v>
+        <v>40.34641585446634</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>10.5649980482419</v>
+        <v>10.56499804530666</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>0.3521453903540544</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0611514874421841</v>
+        <v>0.061151487545212</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>238.3441852836849</v>
+        <v>238.3441852836837</v>
       </c>
       <c r="E98" s="2" t="n">
         <v>5415</v>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>47.3425138522506</v>
+        <v>47.34251386254056</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>12.0016963799206</v>
+        <v>12.00169647970462</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.5303222279471514</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>14.58219559201653</v>
+        <v>14.58219558459895</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>39.89543620445682</v>
+        <v>39.89543650246283</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>15.17051908727227</v>
+        <v>15.17051919777138</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.6861138362604273</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0039333712672736</v>
+        <v>-0.0039333715145379</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>44.30780707882468</v>
+        <v>44.3078070545006</v>
       </c>
       <c r="I100" s="2" t="n">
         <v>36.43845471916114</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.1371158929345433</v>
+        <v>0.1371158929551469</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>217.8255547095977</v>
+        <v>217.8255547095976</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>879</v>
@@ -5802,7 +5802,7 @@
         <v>37.98699343872535</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>18.80190184560387</v>
+        <v>18.80190181495975</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.6084751477765469</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-1.979010483689155</v>
+        <v>-1.979010480598255</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>34.42493330510166</v>
+        <v>34.42493297874039</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>13.30479039063131</v>
+        <v>13.30479054484671</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>0.514791135031893</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0520320577022783</v>
+        <v>0.0520320581966828</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>208.9388482070138</v>
+        <v>208.9388482070135</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>42.85</v>
@@ -5908,7 +5908,7 @@
         <v>42.02876394873476</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>17.00784704889255</v>
+        <v>17.00784705078256</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.5752956218348082</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.1880660907081617</v>
+        <v>0.188066090811181</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>40.58252876442935</v>
+        <v>40.58252879748964</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>15.19398287885846</v>
+        <v>15.19398285918395</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.283038536190505</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.2108127003754232</v>
+        <v>0.2108127003548148</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>47.59814510762627</v>
+        <v>47.59814513697284</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>9.79183020897079</v>
+        <v>9.791830131972061</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.2029733890584552</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.454031267487917</v>
+        <v>-0.4540312674055128</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>41.12935780239491</v>
+        <v>41.12935781247861</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>21.7592091179905</v>
+        <v>21.7592091181699</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>0.2721286845972557</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0308807551060936</v>
+        <v>0.0308807550957894</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>32.64488462725652</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>44.79973580647071</v>
+        <v>44.79973590516246</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.2236491775487307</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0402282386728288</v>
+        <v>0.0402282387243438</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>42.57860504141423</v>
+        <v>42.57860506298858</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>7.104446560858931</v>
+        <v>7.104446458269309</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.406630448438915</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0911280502261935</v>
+        <v>-0.0911280501643818</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>179.6655489594881</v>
+        <v>179.6655489594883</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>18.4</v>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>46.75410530755013</v>
+        <v>46.75410528746463</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>4.383104840893759</v>
+        <v>4.383104756524665</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.3316587358170433</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.136282754270298</v>
+        <v>-0.1362827542187847</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>51.54621104753953</v>
+        <v>51.54621129015008</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>11.73818705462402</v>
+        <v>11.73818704586337</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0.5492099394842883</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.2014240423626525</v>
+        <v>0.2014240415384234</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>155.804205017652</v>
+        <v>155.8042050176516</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>49.15</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>47.12795400677779</v>
+        <v>47.12795405626611</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>10.8383568755214</v>
+        <v>10.83835688232522</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.4022046388043475</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0637214177042897</v>
+        <v>0.0637214176836836</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>46.81199547501882</v>
+        <v>46.81199567266594</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>8.653018608308923</v>
+        <v>8.653018608308919</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.3360373873426625</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.1512677818147805</v>
+        <v>0.1512677816499303</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>50.63805034766321</v>
+        <v>50.63805050570424</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>18.01217968197022</v>
+        <v>18.01217964802071</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>0.515510380048391</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0794412769759196</v>
+        <v>-0.0794412773290734</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.06665102820589</v>
+        <v>42.06665130275145</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>7.749668534210134</v>
+        <v>7.749668470582674</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.4309727197575089</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.1108212976098693</v>
+        <v>0.1108212976922873</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>83.9963318467918</v>
+        <v>83.99633184679178</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>19.65</v>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>46.72785904238908</v>
+        <v>46.72785902654893</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>15.56384328870683</v>
+        <v>15.56384340969484</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>1.242251007067564</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0022391157767619</v>
+        <v>-0.002239115653127</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>

--- a/output/full_scan/batch_seq6_2026-09-24.xlsx
+++ b/output/full_scan/batch_seq6_2026-09-24.xlsx
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>66.66258264529621</v>
+        <v>66.6625826115239</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>20.03638233254001</v>
+        <v>20.0363822045632</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.008072549259758</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0279659058479957</v>
+        <v>0.0279659061596007</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>64.83174483637885</v>
+        <v>64.83174479864655</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>21.49977401398439</v>
+        <v>21.49977405950139</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>8.443961698534848</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1.015667107145368</v>
+        <v>1.015667107334532</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>71.18692326537445</v>
+        <v>71.18692324922169</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>20.36263273942881</v>
+        <v>20.36263277311966</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>2.24580486811646</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.558777395678018</v>
+        <v>1.558777395789289</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6207</v>
+        <v>6196</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>978.3561010787748</v>
+        <v>940.6269194686164</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>125</v>
+        <v>565</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>63.06661889711793</v>
+        <v>65.54270118866148</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14.68035599422468</v>
+        <v>15.66891962145036</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.897767706804681</v>
+        <v>0.9584558643329044</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.320441410945215</v>
+        <v>4.65362449370642</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6196</v>
+        <v>6207</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>940.6269194686192</v>
+        <v>938.3561010787748</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>565</v>
+        <v>125</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>65.54270119928063</v>
+        <v>63.06661889395268</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>15.66891963656409</v>
+        <v>14.68035600196358</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.9584558643329044</v>
+        <v>1.897767706804681</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,11 +782,11 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>4.653624493261205</v>
+        <v>1.320441410989728</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>68.11406773988737</v>
+        <v>68.11406765931157</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>43.05596087803512</v>
+        <v>43.05596089045648</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1.350681376804406</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-1.098817331157905</v>
+        <v>-1.098817330824096</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -845,21 +845,21 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6274</v>
+        <v>6166</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>882.0855854405756</v>
+        <v>856.3184997482543</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1495</v>
+        <v>132</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>56.40010796069737</v>
+        <v>63.59559105150482</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>19.34389638874685</v>
+        <v>22.17453402455245</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.349263704100556</v>
+        <v>1.069878972973927</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>12.90742260212381</v>
+        <v>2.694451169924382</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6182</v>
+        <v>6274</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>869.4724465398691</v>
+        <v>842.0855854405745</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>120.5</v>
+        <v>1495</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>58.26573933002864</v>
+        <v>56.40010795497168</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>15.61506640517012</v>
+        <v>19.34389637098434</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.74736065382166</v>
+        <v>1.349263704100556</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.446095107941201</v>
+        <v>12.90742260190134</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6166</v>
+        <v>6271</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>856.3184997482542</v>
+        <v>839.8220532678628</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>132</v>
+        <v>229</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>63.59559110336602</v>
+        <v>57.91764607239897</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>22.17453390881341</v>
+        <v>24.12880707431705</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.069878972973927</v>
+        <v>0.3509783905401061</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>2.69445116932351</v>
+        <v>-0.2499790627163989</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6271</v>
+        <v>6182</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>839.8220532678628</v>
+        <v>829.4724465398691</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>229</v>
+        <v>120.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>57.91764609460841</v>
+        <v>58.26573932436241</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>24.12880710767694</v>
+        <v>15.61506638242426</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.3509783905401061</v>
+        <v>1.74736065382166</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,11 +1047,11 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.2499790627163989</v>
+        <v>1.446095107985701</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>64.38758131685535</v>
+        <v>64.38758128691919</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>20.97541043588995</v>
+        <v>20.97541040229985</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0.9196191487819916</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>3.835269043957112</v>
+        <v>3.835269044046108</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6291</v>
+        <v>6225</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>776.8305267119989</v>
+        <v>771</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>484</v>
+        <v>50.4</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>56.07705361907149</v>
+        <v>43.51236129759043</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>28.24656523779491</v>
+        <v>30.01213480782318</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.409165748070089</v>
+        <v>10.36975850628528</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.4303852295229902</v>
+        <v>-3.156081681464905</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6225</v>
+        <v>6416</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>771</v>
+        <v>769.0748431689007</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>50.4</v>
+        <v>116.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>43.51236130359737</v>
+        <v>62.65092001242059</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>30.0121348228333</v>
+        <v>30.71079745539794</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>10.36975850628528</v>
+        <v>0.2359423414332075</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-3.156081681531665</v>
+        <v>0.2252700335308999</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6416</v>
+        <v>6426</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>769.0748431689007</v>
+        <v>748.9429054178037</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>116.5</v>
+        <v>389</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>62.65092003189135</v>
+        <v>73.21134644778648</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>30.71079743514897</v>
+        <v>46.69088120719068</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.2359423414332075</v>
+        <v>1.2929223485303</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.2252700332861126</v>
+        <v>5.396445136240061</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6426</v>
+        <v>6291</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>748.9429054178037</v>
+        <v>736.8305267119989</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>389</v>
+        <v>484</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,29 +1294,29 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>73.21134643791333</v>
+        <v>56.07705365631659</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46.69088128627345</v>
+        <v>28.24656545343948</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.2929223485303</v>
+        <v>0.409165748070089</v>
       </c>
       <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>5.396445136484807</v>
+        <v>0.4303852272975277</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>52.12986570728569</v>
+        <v>52.12986569534778</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>42.62926852689309</v>
+        <v>42.62926850175964</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>0.3708707727099934</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-1.198090568105901</v>
+        <v>-1.198090567950138</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>62.63390267570716</v>
+        <v>62.63390269486826</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>23.28980001977224</v>
+        <v>23.28980005703266</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>2.259934107518183</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.6575100139226868</v>
+        <v>0.6575100139004323</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1428,21 +1428,21 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6204</v>
+        <v>6228</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>723.1294712635266</v>
+        <v>724</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>107.5</v>
+        <v>18.7</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>64.36927851827079</v>
+        <v>56.17758027677306</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>23.5186814405634</v>
+        <v>15.4185673640479</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.218678252716549</v>
+        <v>8.688962774626768</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1.361157775118588</v>
+        <v>2.053150232444372</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6292</v>
+        <v>6278</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>714.7329515153431</v>
+        <v>684.6191217153681</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>67</v>
+        <v>212</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>59.61110604525277</v>
+        <v>63.79576572798938</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>29.83339506359597</v>
+        <v>18.3993489583858</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.5071471822056217</v>
+        <v>1.430031148977345</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.0336552234152223</v>
+        <v>1.789170173298464</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6228</v>
+        <v>6438</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>694</v>
+        <v>683.9215222616764</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>18.7</v>
+        <v>157.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>56.17758027949982</v>
+        <v>62.08560623538644</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>15.41856729698002</v>
+        <v>18.47983129133115</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>8.688962774626768</v>
+        <v>2.269757034895909</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>2.05315023241099</v>
+        <v>0.6086841708245725</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6245</v>
+        <v>6204</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>685.7153359639732</v>
+        <v>683.1294712635265</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>85.7</v>
+        <v>107.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>55.81718957299701</v>
+        <v>64.36927854148223</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>20.4142183801418</v>
+        <v>23.51868145354489</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.4982216913324923</v>
+        <v>1.218678252716549</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.4346386188365926</v>
+        <v>1.36115777525211</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6278</v>
+        <v>6292</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>684.6191217153681</v>
+        <v>674.732951515343</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>212</v>
+        <v>67</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>63.79576576256471</v>
+        <v>59.61110605116343</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>18.39934889740825</v>
+        <v>29.8333952912138</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.430031148977345</v>
+        <v>0.5071471822056217</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.789170172630829</v>
+        <v>-0.0336552236043843</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6438</v>
+        <v>6423</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>683.9215222616861</v>
+        <v>657.3005952777112</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>157.5</v>
+        <v>86.8</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>62.08560634492002</v>
+        <v>61.49437366810295</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>18.47983131370662</v>
+        <v>18.51541272088932</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2.269757034895909</v>
+        <v>0.6017233650445784</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.6086841704907591</v>
+        <v>0.2766178293796519</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6173</v>
+        <v>6218</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>683.6060348673063</v>
+        <v>648.8108282475747</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>306.5</v>
+        <v>63.6</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>63.50779682507245</v>
+        <v>73.79643634261519</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>37.54616092363761</v>
+        <v>51.93078586803668</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5615549729494477</v>
+        <v>0.3451807893485021</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.1797555503680925</v>
+        <v>1.469175753523721</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6227</v>
+        <v>6245</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>682.6440202385866</v>
+        <v>645.7153359639734</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>135.5</v>
+        <v>85.7</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>64.06823286879842</v>
+        <v>55.81718952256575</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>30.43473402607072</v>
+        <v>20.41421837045169</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.5644020238586532</v>
+        <v>0.4982216913324923</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.439548690457456</v>
+        <v>0.4346386190368667</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6423</v>
+        <v>6173</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>677.3005952777112</v>
+        <v>643.6060348673063</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>86.8</v>
+        <v>306.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>61.4943737089535</v>
+        <v>63.50779681425375</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>18.51541266220724</v>
+        <v>37.54616086874287</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.6017233650445784</v>
+        <v>0.5615549729494477</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.2766178293574111</v>
+        <v>-0.1797555500343008</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6290</v>
+        <v>6227</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>664.5775541717601</v>
+        <v>642.6440202385866</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>274</v>
+        <v>135.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>58.42997937481366</v>
+        <v>64.06823295006492</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>28.20794361189195</v>
+        <v>30.43473404558108</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.5005337089655052</v>
+        <v>0.5644020238586532</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.5430680888041124</v>
+        <v>1.43954869132538</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6218</v>
+        <v>6189</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>648.8108282475747</v>
+        <v>640.7245478107499</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>63.6</v>
+        <v>49.2</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>73.79643634261519</v>
+        <v>60.44000181689359</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>51.93078586803668</v>
+        <v>13.67839984096187</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.3451807893485021</v>
+        <v>0.7238251276090925</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>1.469175753523721</v>
+        <v>0.2826127596514666</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6275</v>
+        <v>6197</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>641.2369683980836</v>
+        <v>626.757288614293</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>45.9</v>
+        <v>320</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>53.5858527257891</v>
+        <v>57.56544910978222</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>27.5582420087473</v>
+        <v>14.23362220848943</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.3158218194710098</v>
+        <v>0.5544628058873015</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0081198029812019</v>
+        <v>2.284717296414998</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6189</v>
+        <v>6290</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>640.7245478107499</v>
+        <v>624.5775541717605</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>49.2</v>
+        <v>274</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>60.44000185171889</v>
+        <v>58.42997937845858</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>13.6783998427762</v>
+        <v>28.20794359691016</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.7238251276090925</v>
+        <v>0.5005337089655052</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.28261275960696</v>
+        <v>0.5430680888041124</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6197</v>
+        <v>6202</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>626.757288614293</v>
+        <v>623.0894125227733</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>320</v>
+        <v>58.2</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,49 +2142,49 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>57.56544905015739</v>
+        <v>53.00848180909922</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>14.23362223805619</v>
+        <v>11.7860605283677</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5544628058873015</v>
+        <v>0.816426638421937</v>
       </c>
       <c r="K32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>2.284717295858622</v>
+        <v>0.3757278516582537</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6202</v>
+        <v>6275</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>623.0894125227733</v>
+        <v>621.2369683980835</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>58.2</v>
+        <v>45.9</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,29 +2195,29 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>53.00848187069934</v>
+        <v>53.58585277826462</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>11.7860605299908</v>
+        <v>27.55824220543617</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.816426638421937</v>
+        <v>0.3158218194710098</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.3757278515469836</v>
+        <v>0.008119802680767301</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>608.4078607729914</v>
+        <v>608.4078607729913</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>44.7</v>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>46.24721718938914</v>
+        <v>46.24721716411027</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>26.99637984701481</v>
+        <v>26.9963799297368</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.5352959447436444</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.08163990101515189</v>
+        <v>0.0816399009928935</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2276,21 +2276,21 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6270</v>
+        <v>6164</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>582.170624986315</v>
+        <v>579.5083702827676</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>29.7</v>
+        <v>12.25</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>54.12259641874993</v>
+        <v>56.29697336421643</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>11.1947234162119</v>
+        <v>20.87925687190898</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.106854266184539</v>
+        <v>0.8109296247975909</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.2093845028624441</v>
+        <v>0.1093957969047757</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6164</v>
+        <v>6209</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>579.5083702827676</v>
+        <v>570.377286429268</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>12.25</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>56.29697321883355</v>
+        <v>54.75179754727053</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>20.87925688444003</v>
+        <v>24.2543121772284</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.8109296247975909</v>
+        <v>0.5113231867855531</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.1093957969159026</v>
+        <v>-0.2460884420600404</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6209</v>
+        <v>6239</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>570.377286429268</v>
+        <v>558.5424807272306</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>79.90000000000001</v>
+        <v>287</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>54.75179760268308</v>
+        <v>54.98722874357342</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>24.25431224395101</v>
+        <v>9.775126578435078</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.5113231867855531</v>
+        <v>0.4082512880279297</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.2460884423938569</v>
+        <v>1.538349749727842</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6210</v>
+        <v>6270</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>562.2628631187323</v>
+        <v>542.1706249863151</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>17.8</v>
+        <v>29.7</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>51.94672572350459</v>
+        <v>54.12259622361861</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>4.579314586071396</v>
+        <v>11.19472313976482</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>2.038211037459534</v>
+        <v>1.106854266184539</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.2945727899264081</v>
+        <v>0.2093845033297832</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6441</v>
+        <v>6472</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>560.4207383764062</v>
+        <v>525.9710232663094</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>24.9</v>
+        <v>421.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>58.30571125283373</v>
+        <v>50.27569224287209</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>18.74010101154888</v>
+        <v>21.47895966824776</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.6981145641153743</v>
+        <v>0.7738837136404555</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0720673137090254</v>
+        <v>1.263825346662558</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6239</v>
+        <v>6210</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>558.5424807272306</v>
+        <v>522.2628631187323</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>287</v>
+        <v>17.8</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>54.98722877227682</v>
+        <v>51.94672572220852</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>9.775126560589136</v>
+        <v>4.579314773969926</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.4082512880279297</v>
+        <v>2.038211037459534</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1.538349749727842</v>
+        <v>0.2945727899152777</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6236</v>
+        <v>6441</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>527.6100136986141</v>
+        <v>520.4207383764063</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>17.85</v>
+        <v>24.9</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>62.34111175872214</v>
+        <v>58.30571121279586</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>10.7280222251487</v>
+        <v>18.74010103069821</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.6470188605997865</v>
+        <v>0.6981145641153743</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1.982367022323533</v>
+        <v>0.07206731369789909</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6472</v>
+        <v>6236</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>525.9710232663093</v>
+        <v>507.6100136986142</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>421.5</v>
+        <v>17.85</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>50.27569225450445</v>
+        <v>62.34111175872214</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>21.47895961386707</v>
+        <v>10.72802222792324</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.7738837136404555</v>
+        <v>0.6470188605997865</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1.263825345104759</v>
+        <v>1.982367022323533</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6435</v>
+        <v>6432</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>518.6420652514626</v>
+        <v>502.7582762391174</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>253.5</v>
+        <v>60.4</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>52.79101168841078</v>
+        <v>49.27311120016378</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>8.098720347804557</v>
+        <v>20.97058084716383</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.8373601809609074</v>
+        <v>0.5711946558878058</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>2.19272339866041</v>
+        <v>1.082007190547476</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6266</v>
+        <v>6285</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>505.4480800214831</v>
+        <v>498.9103822709467</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>24.9</v>
+        <v>238</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,49 +2778,49 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>49.58365129782495</v>
+        <v>52.99368814470656</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>8.538427430290829</v>
+        <v>19.19277043208252</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6902568812034882</v>
+        <v>1.45478122683924</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0105393242520599</v>
+        <v>1.11422738793159</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6285</v>
+        <v>6194</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>498.9103822709467</v>
+        <v>489.9384265565117</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>238</v>
+        <v>30.55</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,49 +2831,49 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>52.99368818698658</v>
+        <v>65.9119741398849</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>19.19277040414516</v>
+        <v>18.56444069773454</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.45478122683924</v>
+        <v>1.673922534946038</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.114227387709052</v>
+        <v>0.0876780506206233</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, invest_trust_buy_2d, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6233</v>
+        <v>6435</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>482.0695743483041</v>
+        <v>478.6420652514626</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>21.35</v>
+        <v>253.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>55.02064738750971</v>
+        <v>52.79101167753328</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>16.79100262295927</v>
+        <v>8.098720344844233</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.6755558163131483</v>
+        <v>0.8373601809609074</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.1614099976713774</v>
+        <v>2.192723399194521</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6418</v>
+        <v>6414</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>481.5757285346891</v>
+        <v>470.7072010556364</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>34.55</v>
+        <v>374</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,49 +2937,49 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>51.76270038380225</v>
+        <v>42.32645209555573</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>29.62341746619241</v>
+        <v>23.50530759514946</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.1094152202160514</v>
+        <v>0.6067454909135692</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M47" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.1191691628571076</v>
+        <v>1.321266692992577</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6432</v>
+        <v>6266</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>472.7582762391174</v>
+        <v>465.4480800214831</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>60.4</v>
+        <v>24.9</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>49.27311124492324</v>
+        <v>49.58365118902707</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>20.97058091938624</v>
+        <v>8.538427429609374</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.5711946558878058</v>
+        <v>0.6902568812034882</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>1.082007190358317</v>
+        <v>0.0105393242743146</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6414</v>
+        <v>6243</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>470.7072010556364</v>
+        <v>465.3026365477501</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>374</v>
+        <v>39.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,49 +3043,49 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>42.32645212393808</v>
+        <v>49.27003395561079</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>23.5053075816047</v>
+        <v>20.1741029624068</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.6067454909135692</v>
+        <v>3.601378587819686</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>1.321266691768631</v>
+        <v>0.4794189437406344</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6234</v>
+        <v>6244</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>465.4414877189964</v>
+        <v>442.2937938269147</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>37.85</v>
+        <v>23.55</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>54.23099885696675</v>
+        <v>50.72279298124555</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>20.29680774230329</v>
+        <v>16.15653068331635</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.9868653522617546</v>
+        <v>1.680767911299174</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.5286082154111575</v>
+        <v>0.1864583541511312</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6243</v>
+        <v>6233</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>465.3026365477501</v>
+        <v>442.0695743483041</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>39.5</v>
+        <v>21.35</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>49.27003401400765</v>
+        <v>55.02064737555166</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>20.17410291807317</v>
+        <v>16.79100265835989</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>3.601378587819686</v>
+        <v>0.6755558163131483</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.4794189435848568</v>
+        <v>0.1614099976713774</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6241</v>
+        <v>6418</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>鑫永洋</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>465.2246550354751</v>
+        <v>441.5757285346891</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>15.45</v>
+        <v>34.55</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>46.34756962799259</v>
+        <v>51.76270033930709</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>11.48368400662731</v>
+        <v>29.62341748493857</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.9118758669782656</v>
+        <v>0.1094152202160514</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.0664157595723224</v>
+        <v>-0.1191691627458312</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6194</v>
+        <v>6188</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>459.9384265565353</v>
+        <v>438.3472694522597</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>30.55</v>
+        <v>62</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>65.9119741398849</v>
+        <v>33.41576812912675</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>18.56444068287822</v>
+        <v>30.41685909605331</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.673922534946038</v>
+        <v>0.506398935503666</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0876780506540069</v>
+        <v>0.0502098106937023</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6244</v>
+        <v>6237</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>442.2937938269147</v>
+        <v>434.2211869716203</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>23.55</v>
+        <v>37</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>50.72279302367088</v>
+        <v>62.30641632927617</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>16.15653066207243</v>
+        <v>16.87008103914424</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.680767911299174</v>
+        <v>7.103814350115726</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.1864583541066218</v>
+        <v>0.4112636293165364</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6190</v>
+        <v>6234</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>439.6646192834889</v>
+        <v>425.4414877189972</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>68.59999999999999</v>
+        <v>37.85</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>50.77775406772084</v>
+        <v>54.23099891526854</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>12.77166140010748</v>
+        <v>20.29680801630561</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.4768365100193492</v>
+        <v>0.9868653522617546</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.1963630318774921</v>
+        <v>0.5286082149883267</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6187</v>
+        <v>6241</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>425.4533339751006</v>
+        <v>425.2246550354751</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>1195</v>
+        <v>15.45</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>44.7163605359483</v>
+        <v>46.34756943664845</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>13.72835704790159</v>
+        <v>11.48368431540685</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5022947219055958</v>
+        <v>0.9118758669782656</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,11 +3432,11 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-17.41231303429979</v>
+        <v>-0.0664157594088272</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>50.69751589878662</v>
+        <v>50.69751582163631</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>14.93495370666925</v>
+        <v>14.93495373317363</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.3883922134014348</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.1803094858813961</v>
+        <v>0.1803094862152063</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3495,21 +3495,21 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6417</v>
+        <v>6470</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>419.0415423013458</v>
+        <v>419.2708508737744</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>39.4529006043575</v>
+        <v>52.14845599474718</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>38.5024312396481</v>
+        <v>23.62827772636205</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.302163926499033</v>
+        <v>0.3275550635124111</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.1976418200574481</v>
+        <v>0.1311472425687095</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6265</v>
+        <v>6190</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>418.1219098785853</v>
+        <v>399.6646192834892</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>48.45</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>40.50182741793139</v>
+        <v>50.77775415430366</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>20.12072849093827</v>
+        <v>12.77166136283128</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4322829297482632</v>
+        <v>0.4768365100193492</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.4756110685796</v>
+        <v>0.1963630317328475</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6188</v>
+        <v>6187</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>408.3472694522605</v>
+        <v>385.4533339751001</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>62</v>
+        <v>1195</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>33.41576828373668</v>
+        <v>44.71636053976056</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>30.41685899161678</v>
+        <v>13.72835710172023</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.506398935503666</v>
+        <v>0.5022947219055958</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>1</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.050209810382142</v>
+        <v>-17.41231303596892</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6237</v>
+        <v>6417</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>404.2211869716205</v>
+        <v>379.0415423013458</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>62.30641638438206</v>
+        <v>39.45290056541137</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>16.87008103914424</v>
+        <v>38.50243124866704</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>7.103814350115726</v>
+        <v>1.302163926499033</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.4112636293832947</v>
+        <v>0.1976418201242129</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6279</v>
+        <v>6265</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>389.8939760574494</v>
+        <v>378.1219098785853</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>112.5</v>
+        <v>48.45</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>38.37864969904653</v>
+        <v>40.50182741756877</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>35.19637843995342</v>
+        <v>20.12072849093827</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.4544712570610476</v>
+        <v>0.4322829297482632</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.0510056582865265</v>
+        <v>-0.4756110685885009</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6470</v>
+        <v>6261</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>389.2708508737744</v>
+        <v>375.8648785599799</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>43</v>
+        <v>78.3</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>52.14845639667488</v>
+        <v>49.52662477062898</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>23.62827750772938</v>
+        <v>13.22340733910132</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3275550635124111</v>
+        <v>0.7822159383367108</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.1311472423572883</v>
+        <v>0.3924543912837848</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6217</v>
+        <v>6165</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>387.640305997797</v>
+        <v>375.0194527158492</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>170</v>
+        <v>48.95</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>49.3662971753635</v>
+        <v>51.65522469823686</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>13.30479063962005</v>
+        <v>14.35776244274991</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.2828585845508812</v>
+        <v>0.3204236180844755</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.2515590357549234</v>
+        <v>0.1226179575511829</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6174</v>
+        <v>6246</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>385.9387305113407</v>
+        <v>362.5894406864204</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>44.95</v>
+        <v>12.8</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>53.04440237315566</v>
+        <v>49.89878723028504</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>13.75830598057892</v>
+        <v>29.50973024979936</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.9214822437430756</v>
+        <v>0.1892592263872863</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.2859364522161847</v>
+        <v>0.0291312053279579</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6261</v>
+        <v>6183</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>375.86487855998</v>
+        <v>361.439450358852</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>78.3</v>
+        <v>91.3</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>49.52662480919999</v>
+        <v>46.2812959734157</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>13.22340730764942</v>
+        <v>12.93819719573895</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.7822159383367108</v>
+        <v>0.8358651483913635</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.3924543911279985</v>
+        <v>-0.0415195025449918</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6165</v>
+        <v>6167</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>375.0194527158492</v>
+        <v>360.3945452084354</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>48.95</v>
+        <v>10.35</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>51.65522489346169</v>
+        <v>49.22656145456681</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>14.35776235694837</v>
+        <v>11.16743415879401</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.3204236180844755</v>
+        <v>0.9258614980445508</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.1226179572618773</v>
+        <v>0.0407918426943183</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6229</v>
+        <v>6263</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>374.8876730004434</v>
+        <v>357.4687951312504</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>23.7</v>
+        <v>157</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>51.02435907135261</v>
+        <v>45.40923632641721</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10.51247246019061</v>
+        <v>15.9994026000481</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.787894507393719</v>
+        <v>0.3345619315422479</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0464932613910926</v>
+        <v>-0.4189921737297604</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6246</v>
+        <v>6279</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>362.5894406864214</v>
+        <v>349.8939760574495</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>12.8</v>
+        <v>112.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>49.89878730562882</v>
+        <v>38.3786495853063</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>29.50973019397893</v>
+        <v>35.19637855007588</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.1892592263872863</v>
+        <v>0.4544712570610476</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0291312052389402</v>
+        <v>-0.0510056578414497</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6183</v>
+        <v>6217</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>361.439450358852</v>
+        <v>347.6403059977919</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>91.3</v>
+        <v>170</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>46.2812960131929</v>
+        <v>49.36629716924856</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>12.93819722589178</v>
+        <v>13.30479053806468</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.8358651483913635</v>
+        <v>0.2828585845508812</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.0415195026117587</v>
+        <v>-0.2515590356547658</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6263</v>
+        <v>6174</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>357.4687951312504</v>
+        <v>345.9387305113407</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>157</v>
+        <v>44.95</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>45.4092363990372</v>
+        <v>53.04440237315566</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>15.9994026000481</v>
+        <v>13.75830600250693</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.3345619315422479</v>
+        <v>0.9214822437430756</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.4189921739522789</v>
+        <v>0.2859364522273093</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6175</v>
+        <v>6464</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>344.6205923617438</v>
+        <v>341.6280124931552</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>69.7</v>
+        <v>77</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>41.51972473181976</v>
+        <v>45.31154860413452</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>17.27755573500607</v>
+        <v>21.17974310188868</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4388308517117974</v>
+        <v>0.0258545151225515</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.4208327071244833</v>
+        <v>0.0017758927649053</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6464</v>
+        <v>6198</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>341.6280124931552</v>
+        <v>336.4797730940201</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>77</v>
+        <v>19.4</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>45.311548594078</v>
+        <v>52.94284093096098</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>21.1797430643264</v>
+        <v>8.39107885512303</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.0258545151225515</v>
+        <v>0.5176056641686142</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0017758927871598</v>
+        <v>0.7252487583974783</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6198</v>
+        <v>6229</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>336.4797730940198</v>
+        <v>334.887673000443</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>19.4</v>
+        <v>23.7</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>52.94284092517208</v>
+        <v>51.02435900280756</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>8.391078879284182</v>
+        <v>10.51247239227078</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5176056641686142</v>
+        <v>1.787894507393719</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.725248758542131</v>
+        <v>0.0464932614244739</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6167</v>
+        <v>6269</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>330.3945452084353</v>
+        <v>330.0840289244618</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>10.35</v>
+        <v>64.8</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>49.22656237582801</v>
+        <v>48.51220894355768</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>11.16743399310105</v>
+        <v>13.07883756773208</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.9258614980445508</v>
+        <v>0.2668226654170578</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.040791842503621</v>
+        <v>-0.4559629286033612</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6269</v>
+        <v>6405</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>330.0840289244618</v>
+        <v>328.3159040054463</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>64.8</v>
+        <v>41.45</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>48.51220891310973</v>
+        <v>54.4374863753659</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>13.07883754643277</v>
+        <v>22.19787641731693</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.2668226654170578</v>
+        <v>0.7982058273106563</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.4559629283140562</v>
+        <v>0.4999337154894016</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6405</v>
+        <v>6451</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>328.3159040054463</v>
+        <v>326.7347828857845</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>41.45</v>
+        <v>412</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>54.43748638967728</v>
+        <v>45.15748998378626</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>22.19787643486348</v>
+        <v>8.165077360048784</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.7982058273106563</v>
+        <v>0.2402832464634738</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.4999337154560176</v>
+        <v>-1.136527823731039</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6451</v>
+        <v>6281</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>326.7347828857846</v>
+        <v>322.3023664125197</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>412</v>
+        <v>51</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>45.15749001467479</v>
+        <v>43.19196886924206</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>8.165077429541601</v>
+        <v>9.44472511481046</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.2402832464634738</v>
+        <v>1.246051462242154</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-1.136527824621186</v>
+        <v>-0.0266107557776273</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6281</v>
+        <v>6446</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>322.302366412524</v>
+        <v>321.8016867489027</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>51</v>
+        <v>1155</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>43.19196893741344</v>
+        <v>37.70268301040743</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>9.444725035095598</v>
+        <v>19.91332233501342</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.246051462242154</v>
+        <v>0.3363047400516636</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0266107557776273</v>
+        <v>-17.23431402341906</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6446</v>
+        <v>6442</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>321.8016867489027</v>
+        <v>319.4928674430856</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1155</v>
+        <v>1530</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>37.70268303386835</v>
+        <v>46.36378423009354</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>19.91332229994196</v>
+        <v>14.53493400236996</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.3363047400516636</v>
+        <v>0.335084557587092</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-17.2343140257558</v>
+        <v>-23.03758894649784</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6442</v>
+        <v>6175</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>319.4928674430853</v>
+        <v>304.6205923617438</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>1530</v>
+        <v>69.7</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>46.3637842240508</v>
+        <v>41.51972468715783</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>14.53493405065067</v>
+        <v>17.27755573469414</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.335084557587092</v>
+        <v>0.4388308517117974</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-23.03758894672034</v>
+        <v>0.4208327072468796</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6170</v>
+        <v>6272</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>317.7149733908975</v>
+        <v>301.1287513341082</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>48.4</v>
+        <v>25.3</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>55.0574647690319</v>
+        <v>42.92351276222081</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>15.63255880519765</v>
+        <v>29.6378401703032</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.7633969650774827</v>
+        <v>0.3033643822283974</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.0125232577130676</v>
+        <v>-0.3388584251288025</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6259</v>
+        <v>6170</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>316.9186290747091</v>
+        <v>297.7149733908975</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>29.15</v>
+        <v>48.4</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>47.24901165534814</v>
+        <v>55.05746490579277</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>9.33195505922318</v>
+        <v>15.63255878848084</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.1999522804176186</v>
+        <v>0.7633969650774827</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.1516932618448554</v>
+        <v>-0.0125232578465917</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6272</v>
+        <v>6277</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>301.1287513341082</v>
+        <v>293.1407128457347</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>25.3</v>
+        <v>77.8</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>42.92351270016616</v>
+        <v>47.3337223392534</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>29.6378401882417</v>
+        <v>17.1019109472108</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.3033643822283974</v>
+        <v>0.4130871344689618</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.3388584251955637</v>
+        <v>-0.0036963857785711</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6277</v>
+        <v>6163</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>293.1407128457347</v>
+        <v>290.4610578039632</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>77.8</v>
+        <v>41.4</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>47.33372239767546</v>
+        <v>49.91367463266737</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>17.10191097450986</v>
+        <v>11.00547877705841</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4130871344689618</v>
+        <v>1.2360394854377</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,11 +4969,11 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0036963859566039</v>
+        <v>0.1973740400339605</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -4990,7 +4990,7 @@
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>288.454822621746</v>
+        <v>288.4548226217468</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>82.3</v>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>45.75095641830281</v>
+        <v>45.75095612002313</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>13.94461235866969</v>
+        <v>13.94461236375281</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.6403460571916633</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.2965934572187685</v>
+        <v>0.2965934575525913</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>286.7034726959216</v>
+        <v>286.7034726959217</v>
       </c>
       <c r="E87" s="2" t="n">
         <v>38.7</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>50.49085074411749</v>
+        <v>50.49085065345289</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>12.55513224158592</v>
+        <v>12.55513229844308</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>1.62343459484132</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.1213603345035025</v>
+        <v>0.121360334548011</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>283.8633905955882</v>
+        <v>283.8633905955883</v>
       </c>
       <c r="E88" s="2" t="n">
         <v>209.5</v>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>41.6234135494498</v>
+        <v>41.62341357653133</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>12.15538151427203</v>
+        <v>12.15538152877381</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>0.332508490117131</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0108765461737343</v>
+        <v>-0.0108765456173891</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>280.3097969186824</v>
+        <v>280.3097969186821</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>96.8</v>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>46.09711559661935</v>
+        <v>46.09711521401546</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>10.92089896110865</v>
+        <v>10.92089897909016</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.641946204768259</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0199639993654718</v>
+        <v>0.0199640007007245</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>279.7222835757408</v>
+        <v>279.7222835757412</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>113</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>53.77027263640132</v>
+        <v>53.77027256738236</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>13.87008616059449</v>
+        <v>13.87008616732989</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>0.6258834396525222</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.4863430402150366</v>
+        <v>0.4863430409939364</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5244,21 +5244,21 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6177</v>
+        <v>6259</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>272.3237921966168</v>
+        <v>276.9186290747091</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>46.2</v>
+        <v>29.15</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>41.60083912676578</v>
+        <v>47.24901173244205</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>17.57008104591565</v>
+        <v>9.331955039960674</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.7003234123180839</v>
+        <v>0.1999522804176186</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.1415884158682428</v>
+        <v>0.1516932618448554</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6415</v>
+        <v>6177</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>266.3991153106608</v>
+        <v>272.3237921966169</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>425.5</v>
+        <v>46.2</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,25 +5322,25 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>48.46548197560504</v>
+        <v>41.60083959520327</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>9.678042294048854</v>
+        <v>17.570081989431</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4839489536893613</v>
+        <v>0.7003234123180839</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>3.296308895384819</v>
+        <v>-0.1415884171589934</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5350,21 +5350,21 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6185</v>
+        <v>6415</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>263.5818722190636</v>
+        <v>266.3991153106608</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>12.45</v>
+        <v>425.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,49 +5375,49 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>38.90267472591915</v>
+        <v>48.46548191839932</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>25.06707505837024</v>
+        <v>9.678042344682526</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.5733843133584536</v>
+        <v>0.4839489536893613</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0360409968286455</v>
+        <v>3.296308895496102</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6163</v>
+        <v>6412</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>260.4610578039632</v>
+        <v>248.4185516522064</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>41.4</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>49.91367467182027</v>
+        <v>37.79188013040136</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>11.00547871075513</v>
+        <v>26.03791664100356</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.2360394854377</v>
+        <v>0.5826557882460266</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.1973740399671954</v>
+        <v>0.1685064759510397</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6412</v>
+        <v>6192</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>248.4185516522064</v>
+        <v>241.7573065478446</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>110.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>37.79188046827763</v>
+        <v>38.96565016862916</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>26.03791649979354</v>
+        <v>27.41533889263207</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5826557882460266</v>
+        <v>0.4247648389105568</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.1685064757284906</v>
+        <v>-0.1428655263548504</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6192</v>
+        <v>6184</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>241.7573065478444</v>
+        <v>227.7043836813468</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>110.5</v>
+        <v>40.3</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>38.96565007686494</v>
+        <v>44.3078070545006</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>27.41533883992354</v>
+        <v>36.43845475996632</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.4247648389105568</v>
+        <v>0.230954563436029</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.1428655265773857</v>
+        <v>0.1371158929551469</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5562,21 +5562,21 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6220</v>
+        <v>6185</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>239.0563385192113</v>
+        <v>223.5818722190636</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>25.25</v>
+        <v>12.45</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>40.34641585446634</v>
+        <v>38.9026751449344</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>10.56499804530666</v>
+        <v>25.06707504146626</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.3521453903540544</v>
+        <v>0.5733843133584536</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>2</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.061151487545212</v>
+        <v>0.0360409966728663</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6223</v>
+        <v>6409</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>238.3441852836837</v>
+        <v>217.8255547095952</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>5415</v>
+        <v>879</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>47.34251386254056</v>
+        <v>37.98699331430593</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>12.00169647970462</v>
+        <v>18.80190188827629</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.5303222279471514</v>
+        <v>0.6084751477765469</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>14.58219558459895</v>
+        <v>-1.979010477260189</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6474</v>
+        <v>6222</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>228.0903613714612</v>
+        <v>209.6655489594881</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>35.55</v>
+        <v>18.4</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>39.89543650246283</v>
+        <v>46.75410530269195</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>15.17051919777138</v>
+        <v>4.383104653122451</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.6861138362604273</v>
+        <v>0.3316587358170433</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0039333715145379</v>
+        <v>-0.1362827542410348</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6184</v>
+        <v>6282</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>227.7043836813466</v>
+        <v>208.9388482070138</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>40.3</v>
+        <v>42.85</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>44.3078070545006</v>
+        <v>42.02876394873476</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>36.43845471916114</v>
+        <v>17.00784694733757</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.230954563436029</v>
+        <v>0.5752956218348082</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.1371158929551469</v>
+        <v>0.1880660909224483</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6409</v>
+        <v>6220</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>217.8255547095976</v>
+        <v>199.0563385192113</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>879</v>
+        <v>25.25</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>37.98699343872535</v>
+        <v>40.34641521279349</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>18.80190181495975</v>
+        <v>10.564998027848</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6084751477765469</v>
+        <v>0.3521453903540544</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-1.979010480598255</v>
+        <v>0.0611514878011362</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6465</v>
+        <v>6223</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>215.2652422590988</v>
+        <v>198.3441852836838</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>41.65</v>
+        <v>5415</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>34.42493297874039</v>
+        <v>47.34251389087935</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>13.30479054484671</v>
+        <v>12.00169645797498</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.514791135031893</v>
+        <v>0.5303222279471514</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0520320581966828</v>
+        <v>14.58219558548844</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6282</v>
+        <v>6283</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>208.9388482070135</v>
+        <v>192.2737447752444</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>42.85</v>
+        <v>18.85</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>42.02876394873476</v>
+        <v>41.12935784356573</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>17.00784705078256</v>
+        <v>21.75920912489022</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.5752956218348082</v>
+        <v>0.2721286845972557</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.188066090811181</v>
+        <v>0.0308807550957894</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6208</v>
+        <v>6474</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>206.3717116009259</v>
+        <v>188.0903613714612</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>74.3</v>
+        <v>35.55</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>40.58252879748964</v>
+        <v>39.89543607133883</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>15.19398285918395</v>
+        <v>15.17051919777138</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.283038536190505</v>
+        <v>0.6861138362604273</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.2108127003548148</v>
+        <v>-0.0039333713476361</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6419</v>
+        <v>6216</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>205.9716635143944</v>
+        <v>186.5728803333345</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>149</v>
+        <v>19.55</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>47.59814513697284</v>
+        <v>32.64488451358282</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>9.791830131972061</v>
+        <v>44.7997360380864</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.2029733890584552</v>
+        <v>0.2236491775487307</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.4540312674055128</v>
+        <v>0.0402282387799796</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6283</v>
+        <v>6208</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>192.2737447752444</v>
+        <v>186.3717116009259</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>18.85</v>
+        <v>74.3</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>41.12935781247861</v>
+        <v>40.58252876581918</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>21.7592091181699</v>
+        <v>15.19398282270926</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.2721286845972557</v>
+        <v>0.283038536190505</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0308807550957894</v>
+        <v>0.2108127004772093</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6216</v>
+        <v>6161</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>捷波</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>186.5728803333345</v>
+        <v>185.804205017652</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>19.55</v>
+        <v>49.15</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>32.64488462725652</v>
+        <v>47.1279540064177</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>44.79973590516246</v>
+        <v>10.83835690120524</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.2236491775487307</v>
+        <v>0.4022046388043475</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,11 +6135,11 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0402282387243438</v>
+        <v>0.0637214178172059</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>42.57860506298858</v>
+        <v>42.57860500858608</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>7.104446458269309</v>
+        <v>7.104446471130253</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.406630448438915</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0911280501643818</v>
+        <v>-0.0911280499863422</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6222</v>
+        <v>6465</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>179.6655489594883</v>
+        <v>175.2652422590988</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>18.4</v>
+        <v>41.65</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>46.75410528746463</v>
+        <v>34.42493319694726</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>4.383104756524665</v>
+        <v>13.30479049546203</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.3316587358170433</v>
+        <v>0.514791135031893</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.1362827542187847</v>
+        <v>0.0520320578724973</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6462</v>
+        <v>6419</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>176.8008097181369</v>
+        <v>165.9716635143944</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>99.7</v>
+        <v>149</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,49 +6276,49 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>51.54621129015008</v>
+        <v>47.59814510703222</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>11.73818704586337</v>
+        <v>9.791830152220156</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5492099394842883</v>
+        <v>0.2029733890584552</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.2014240415384234</v>
+        <v>-0.4540312668936635</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6161</v>
+        <v>6203</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>捷波</t>
+          <t>海韻電</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>155.8042050176516</v>
+        <v>156.8471884399789</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>49.15</v>
+        <v>59.6</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>47.12795405626611</v>
+        <v>42.06665094795412</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>10.83835688232522</v>
+        <v>7.749668698014489</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.4022046388043475</v>
+        <v>0.4309727197575089</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>2</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0637214176836836</v>
+        <v>0.1108212981151282</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6411</v>
+        <v>6176</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>147.8897659861489</v>
+        <v>139.5218620707787</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>46.81199567266594</v>
+        <v>50.63805033550621</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>8.653018608308919</v>
+        <v>18.01217978233533</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.3360373873426625</v>
+        <v>0.515510380048391</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.1512677816499303</v>
+        <v>-0.07944127656626861</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6176</v>
+        <v>6462</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>139.5218620707787</v>
+        <v>136.8008097181372</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>91.8</v>
+        <v>99.7</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,49 +6435,49 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>50.63805050570424</v>
+        <v>51.54621111774532</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>18.01217964802071</v>
+        <v>11.73818726756863</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.515510380048391</v>
+        <v>0.5492099394842883</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M113" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0794412773290734</v>
+        <v>0.2014240419835171</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6203</v>
+        <v>6411</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>126.8471884399789</v>
+        <v>127.8897659861489</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>59.6</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.06665130275145</v>
+        <v>46.81199547150865</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>7.749668470582674</v>
+        <v>8.653018537151107</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.4309727197575089</v>
+        <v>0.3360373873426625</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>2</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.1108212976922873</v>
+        <v>0.151267782206295</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>83.99633184679178</v>
+        <v>113.9963318467911</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>19.65</v>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>46.72785902654893</v>
+        <v>46.72785919713524</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>15.56384340969484</v>
+        <v>15.56384387507603</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>1.242251007067564</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.002239115653127</v>
+        <v>-0.0022391155418597</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>

--- a/output/full_scan/batch_seq6_2026-09-24.xlsx
+++ b/output/full_scan/batch_seq6_2026-09-24.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1365.600643930045</v>
+        <v>1325.600643930045</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>595</v>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1064</v>
+        <v>1024</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>73.59999999999999</v>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>986.4580486811648</v>
+        <v>1016.458048681165</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>81.3</v>
@@ -686,21 +686,21 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6196</v>
+        <v>6207</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>940.6269194686164</v>
+        <v>978.3561010787748</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>565</v>
+        <v>125</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>65.54270118866148</v>
+        <v>63.06661889395268</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15.66891962145036</v>
+        <v>14.68035600196358</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.9584558643329044</v>
+        <v>1.897767706804681</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>4.65362449370642</v>
+        <v>1.320441410989728</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6207</v>
+        <v>6196</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>938.3561010787748</v>
+        <v>900.6269194686163</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>125</v>
+        <v>565</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>63.06661889395268</v>
+        <v>65.54270118866148</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>14.68035600196358</v>
+        <v>15.66891962145036</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.897767706804681</v>
+        <v>0.9584558643329044</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.320441410989728</v>
+        <v>4.65362449370642</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6214</v>
+        <v>6274</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>888.0837061439793</v>
+        <v>882.0855854405745</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>190.5</v>
+        <v>1495</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>68.11406765931157</v>
+        <v>56.40010795497168</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>43.05596089045648</v>
+        <v>19.34389637098434</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.350681376804406</v>
+        <v>1.349263704100556</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-1.098817330824096</v>
+        <v>12.90742260190134</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6166</v>
+        <v>6182</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>856.3184997482543</v>
+        <v>869.4724465398691</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>132</v>
+        <v>120.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>63.59559105150482</v>
+        <v>58.26573932436241</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>22.17453402455245</v>
+        <v>15.61506638242426</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.069878972973927</v>
+        <v>1.74736065382166</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>1</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>2.694451169924382</v>
+        <v>1.446095107985701</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6274</v>
+        <v>6214</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>842.0855854405745</v>
+        <v>848.0837061439793</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1495</v>
+        <v>190.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>56.40010795497168</v>
+        <v>68.11406765931157</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>19.34389637098434</v>
+        <v>43.05596089045648</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.349263704100556</v>
+        <v>1.350681376804406</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>12.90742260190134</v>
+        <v>-1.098817330824096</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6271</v>
+        <v>6166</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>839.8220532678628</v>
+        <v>816.3184997482543</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>229</v>
+        <v>132</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>57.91764607239897</v>
+        <v>63.59559105150482</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>24.12880707431705</v>
+        <v>22.17453402455245</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.3509783905401061</v>
+        <v>1.069878972973927</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.2499790627163989</v>
+        <v>2.694451169924382</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6182</v>
+        <v>6168</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>829.4724465398691</v>
+        <v>809.7712412476581</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>120.5</v>
+        <v>44</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>58.26573932436241</v>
+        <v>77.5727119667022</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>15.61506638242426</v>
+        <v>45.69341910607962</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.74736065382166</v>
+        <v>0.577124124765807</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>1</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>1.446095107985701</v>
+        <v>1.404366011122366</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6257</v>
+        <v>6271</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>783.0898562793354</v>
+        <v>799.8220532678628</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>64.38758128691919</v>
+        <v>57.91764607239897</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>20.97541040229985</v>
+        <v>24.12880707431705</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.9196191487819916</v>
+        <v>0.3509783905401061</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>3.835269044046108</v>
+        <v>-0.2499790627163989</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6225</v>
+        <v>6291</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>771</v>
+        <v>776.8305267119989</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>50.4</v>
+        <v>484</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>43.51236129759043</v>
+        <v>56.07705365631659</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>30.01213480782318</v>
+        <v>28.24656545343948</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>10.36975850628528</v>
+        <v>0.409165748070089</v>
       </c>
       <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-3.156081681464905</v>
+        <v>0.4303852272975277</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6416</v>
+        <v>6443</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>769.0748431689007</v>
+        <v>756.5993410751819</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>116.5</v>
+        <v>28.25</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>62.65092001242059</v>
+        <v>62.63390269486826</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>30.71079745539794</v>
+        <v>23.28980005703266</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.2359423414332075</v>
+        <v>2.259934107518183</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.2252700335308999</v>
+        <v>0.6575100139004323</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6426</v>
+        <v>6257</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>748.9429054178037</v>
+        <v>743.0898562793354</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>389</v>
+        <v>243</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>73.21134644778648</v>
+        <v>64.38758128691919</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>46.69088120719068</v>
+        <v>20.97541040229985</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.2929223485303</v>
+        <v>0.9196191487819916</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>5.396445136240061</v>
+        <v>3.835269044046108</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1269,21 +1269,21 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6291</v>
+        <v>6225</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>736.8305267119989</v>
+        <v>731</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>484</v>
+        <v>50.4</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,49 +1294,49 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>56.07705365631659</v>
+        <v>43.51236129759043</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>28.24656545343948</v>
+        <v>30.01213480782318</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.409165748070089</v>
+        <v>10.36975850628528</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.4303852272975277</v>
+        <v>-3.156081681464905</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6224</v>
+        <v>6416</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>734.4020503562305</v>
+        <v>729.0748431689007</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>82.2</v>
+        <v>116.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>52.12986569534778</v>
+        <v>62.65092001242059</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>42.62926850175964</v>
+        <v>30.71079745539794</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.3708707727099934</v>
+        <v>0.2359423414332075</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-1.198090567950138</v>
+        <v>0.2252700335308999</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6443</v>
+        <v>6204</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>726.5993410751819</v>
+        <v>723.1294712635265</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>28.25</v>
+        <v>107.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>62.63390269486826</v>
+        <v>64.36927854148223</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>23.28980005703266</v>
+        <v>23.51868145354489</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.259934107518183</v>
+        <v>1.218678252716549</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.6575100139004323</v>
+        <v>1.36115777525211</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6228</v>
+        <v>6292</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>724</v>
+        <v>714.732951515343</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>18.7</v>
+        <v>67</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>56.17758027677306</v>
+        <v>59.61110605116343</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>15.4185673640479</v>
+        <v>29.8333952912138</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>8.688962774626768</v>
+        <v>0.5071471822056217</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>2.053150232444372</v>
+        <v>-0.0336552236043843</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6278</v>
+        <v>6426</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>684.6191217153681</v>
+        <v>708.9429054178037</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>212</v>
+        <v>389</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>63.79576572798938</v>
+        <v>73.21134644778648</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>18.3993489583858</v>
+        <v>46.69088120719068</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.430031148977345</v>
+        <v>1.2929223485303</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.789170173298464</v>
+        <v>5.396445136240061</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6438</v>
+        <v>6224</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>683.9215222616764</v>
+        <v>694.4020503562305</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>157.5</v>
+        <v>82.2</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>62.08560623538644</v>
+        <v>52.12986569534778</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>18.47983129133115</v>
+        <v>42.62926850175964</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.269757034895909</v>
+        <v>0.3708707727099934</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.6086841708245725</v>
+        <v>-1.198090567950138</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6204</v>
+        <v>6228</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>683.1294712635265</v>
+        <v>694</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>107.5</v>
+        <v>18.7</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>64.36927854148223</v>
+        <v>56.17758027677306</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>23.51868145354489</v>
+        <v>15.4185673640479</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.218678252716549</v>
+        <v>8.688962774626768</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>1.36115777525211</v>
+        <v>2.053150232444372</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6292</v>
+        <v>6245</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>674.732951515343</v>
+        <v>685.7153359639734</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>67</v>
+        <v>85.7</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>59.61110605116343</v>
+        <v>55.81718952256575</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>29.8333952912138</v>
+        <v>20.41421837045169</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5071471822056217</v>
+        <v>0.4982216913324923</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>2</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.0336552236043843</v>
+        <v>0.4346386190368667</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6423</v>
+        <v>6173</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>657.3005952777112</v>
+        <v>683.6060348673063</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>86.8</v>
+        <v>306.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>61.49437366810295</v>
+        <v>63.50779681425375</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>18.51541272088932</v>
+        <v>37.54616086874287</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.6017233650445784</v>
+        <v>0.5615549729494477</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.2766178293796519</v>
+        <v>-0.1797555500343008</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6218</v>
+        <v>6227</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>648.8108282475747</v>
+        <v>682.6440202385866</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>63.6</v>
+        <v>135.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>73.79643634261519</v>
+        <v>64.06823295006492</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>51.93078586803668</v>
+        <v>30.43473404558108</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.3451807893485021</v>
+        <v>0.5644020238586532</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.469175753523721</v>
+        <v>1.43954869132538</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6245</v>
+        <v>6226</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>645.7153359639734</v>
+        <v>680.9556227184395</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>85.7</v>
+        <v>44</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>55.81718952256575</v>
+        <v>69.26643488441633</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>20.41421837045169</v>
+        <v>45.63164488264253</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4982216913324923</v>
+        <v>0.0952281336412283</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.4346386190368667</v>
+        <v>0.6787625858140807</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6173</v>
+        <v>6423</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>643.6060348673063</v>
+        <v>677.3005952777112</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>306.5</v>
+        <v>86.8</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>63.50779681425375</v>
+        <v>61.49437366810295</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>37.54616086874287</v>
+        <v>18.51541272088932</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5615549729494477</v>
+        <v>0.6017233650445784</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.1797555500343008</v>
+        <v>0.2766178293796519</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6227</v>
+        <v>6290</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>642.6440202385866</v>
+        <v>664.5775541717605</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>135.5</v>
+        <v>274</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>64.06823295006492</v>
+        <v>58.42997937845858</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>30.43473404558108</v>
+        <v>28.20794359691016</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.5644020238586532</v>
+        <v>0.5005337089655052</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.43954869132538</v>
+        <v>0.5430680888041124</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6189</v>
+        <v>6218</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>640.7245478107499</v>
+        <v>648.8108282475747</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>49.2</v>
+        <v>63.6</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>60.44000181689359</v>
+        <v>73.79643634261519</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>13.67839984096187</v>
+        <v>51.93078586803668</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7238251276090925</v>
+        <v>0.3451807893485021</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.2826127596514666</v>
+        <v>1.469175753523721</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6197</v>
+        <v>6278</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>626.757288614293</v>
+        <v>644.6191217153681</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>320</v>
+        <v>212</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>57.56544910978222</v>
+        <v>63.79576572798938</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>14.23362220848943</v>
+        <v>18.3993489583858</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5544628058873015</v>
+        <v>1.430031148977345</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>2.284717296414998</v>
+        <v>1.789170173298464</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6290</v>
+        <v>6438</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>624.5775541717605</v>
+        <v>643.9215222616764</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>274</v>
+        <v>157.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>58.42997937845858</v>
+        <v>62.08560623538644</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>28.20794359691016</v>
+        <v>18.47983129133115</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.5005337089655052</v>
+        <v>2.269757034895909</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.5430680888041124</v>
+        <v>0.6086841708245725</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6202</v>
+        <v>6275</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>623.0894125227733</v>
+        <v>641.2369683980835</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>58.2</v>
+        <v>45.9</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,49 +2142,49 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>53.00848180909922</v>
+        <v>53.58585277826462</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>11.7860605283677</v>
+        <v>27.55824220543617</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.816426638421937</v>
+        <v>0.3158218194710098</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.3757278516582537</v>
+        <v>0.008119802680767301</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6275</v>
+        <v>6164</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>621.2369683980835</v>
+        <v>609.5083702827676</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>45.9</v>
+        <v>12.25</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>53.58585277826462</v>
+        <v>56.29697336421643</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>27.55824220543617</v>
+        <v>20.87925687190898</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.3158218194710098</v>
+        <v>0.8109296247975909</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.008119802680767301</v>
+        <v>0.1093957969047757</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6201</v>
+        <v>6189</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>608.4078607729913</v>
+        <v>600.7245478107499</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>44.7</v>
+        <v>49.2</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>46.24721716411027</v>
+        <v>60.44000181689359</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>26.9963799297368</v>
+        <v>13.67839984096187</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.5352959447436444</v>
+        <v>0.7238251276090925</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0816399009928935</v>
+        <v>0.2826127596514666</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6164</v>
+        <v>6197</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>579.5083702827676</v>
+        <v>586.757288614293</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>12.25</v>
+        <v>320</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>56.29697336421643</v>
+        <v>57.56544910978222</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>20.87925687190898</v>
+        <v>14.23362220848943</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.8109296247975909</v>
+        <v>0.5544628058873015</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.1093957969047757</v>
+        <v>2.284717296414998</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6209</v>
+        <v>6202</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>570.377286429268</v>
+        <v>583.0894125227733</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>79.90000000000001</v>
+        <v>58.2</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,49 +2354,49 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>54.75179754727053</v>
+        <v>53.00848180909922</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>24.2543121772284</v>
+        <v>11.7860605283677</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5113231867855531</v>
+        <v>0.816426638421937</v>
       </c>
       <c r="K36" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L36" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.2460884420600404</v>
+        <v>0.3757278516582537</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6239</v>
+        <v>6270</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>558.5424807272306</v>
+        <v>582.1706249863151</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>287</v>
+        <v>29.7</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>54.98722874357342</v>
+        <v>54.12259622361861</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>9.775126578435078</v>
+        <v>11.19472313976482</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4082512880279297</v>
+        <v>1.106854266184539</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.538349749727842</v>
+        <v>0.2093845033297832</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6270</v>
+        <v>6201</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>542.1706249863151</v>
+        <v>568.4078607729913</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>29.7</v>
+        <v>44.7</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>54.12259622361861</v>
+        <v>46.24721716411027</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>11.19472313976482</v>
+        <v>26.9963799297368</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.106854266184539</v>
+        <v>0.5352959447436444</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.2093845033297832</v>
+        <v>0.0816399009928935</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6472</v>
+        <v>6210</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>525.9710232663094</v>
+        <v>562.2628631187323</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>421.5</v>
+        <v>17.8</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>50.27569224287209</v>
+        <v>51.94672572220852</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>21.47895966824776</v>
+        <v>4.579314773969926</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.7738837136404555</v>
+        <v>2.038211037459534</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1.263825346662558</v>
+        <v>0.2945727899152777</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6210</v>
+        <v>6441</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>522.2628631187323</v>
+        <v>560.4207383764063</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>17.8</v>
+        <v>24.9</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>51.94672572220852</v>
+        <v>58.30571121279586</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>4.579314773969926</v>
+        <v>18.74010103069821</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2.038211037459534</v>
+        <v>0.6981145641153743</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.2945727899152777</v>
+        <v>0.07206731369789909</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6441</v>
+        <v>6209</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>520.4207383764063</v>
+        <v>530.377286429268</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>24.9</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>58.30571121279586</v>
+        <v>54.75179754727053</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>18.74010103069821</v>
+        <v>24.2543121772284</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.6981145641153743</v>
+        <v>0.5113231867855531</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>1</v>
@@ -2637,11 +2637,11 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.07206731369789909</v>
+        <v>-0.2460884420600404</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>507.6100136986142</v>
+        <v>527.6100136986141</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>17.85</v>
@@ -2700,21 +2700,21 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6432</v>
+        <v>6435</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>502.7582762391174</v>
+        <v>518.6420652514626</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>60.4</v>
+        <v>253.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>49.27311120016378</v>
+        <v>52.79101167753328</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>20.97058084716383</v>
+        <v>8.098720344844233</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.5711946558878058</v>
+        <v>0.8373601809609074</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>1.082007190547476</v>
+        <v>2.192723399194521</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6285</v>
+        <v>6239</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>498.9103822709467</v>
+        <v>518.5424807272306</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>238</v>
+        <v>287</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,49 +2778,49 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>52.99368814470656</v>
+        <v>54.98722874357342</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>19.19277043208252</v>
+        <v>9.775126578435078</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.45478122683924</v>
+        <v>0.4082512880279297</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>1.11422738793159</v>
+        <v>1.538349749727842</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6194</v>
+        <v>6266</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>489.9384265565117</v>
+        <v>505.4480800214831</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>30.55</v>
+        <v>24.9</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>65.9119741398849</v>
+        <v>49.58365118902707</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>18.56444069773454</v>
+        <v>8.538427429609374</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.673922534946038</v>
+        <v>0.6902568812034882</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0876780506206233</v>
+        <v>0.0105393242743146</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6435</v>
+        <v>6243</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>478.6420652514626</v>
+        <v>495.3026365477501</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>253.5</v>
+        <v>39.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>52.79101167753328</v>
+        <v>49.27003395561079</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>8.098720344844233</v>
+        <v>20.1741029624068</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.8373601809609074</v>
+        <v>3.601378587819686</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>2.192723399194521</v>
+        <v>0.4794189437406344</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6414</v>
+        <v>6472</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>470.7072010556364</v>
+        <v>485.9710232663094</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>374</v>
+        <v>421.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,49 +2937,49 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>42.32645209555573</v>
+        <v>50.27569224287209</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>23.50530759514946</v>
+        <v>21.47895966824776</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.6067454909135692</v>
+        <v>0.7738837136404555</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>1.321266692992577</v>
+        <v>1.263825346662558</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6266</v>
+        <v>6233</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>465.4480800214831</v>
+        <v>482.0695743483041</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>24.9</v>
+        <v>21.35</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>49.58365118902707</v>
+        <v>55.02064737555166</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>8.538427429609374</v>
+        <v>16.79100265835989</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6902568812034882</v>
+        <v>0.6755558163131483</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0105393242743146</v>
+        <v>0.1614099976713774</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6243</v>
+        <v>6418</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>465.3026365477501</v>
+        <v>481.5757285346891</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>39.5</v>
+        <v>34.55</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>49.27003395561079</v>
+        <v>51.76270033930709</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>20.1741029624068</v>
+        <v>29.62341748493857</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>3.601378587819686</v>
+        <v>0.1094152202160514</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.4794189437406344</v>
+        <v>-0.1191691627458312</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6244</v>
+        <v>6432</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>442.2937938269147</v>
+        <v>472.7582762391174</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>23.55</v>
+        <v>60.4</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>50.72279298124555</v>
+        <v>49.27311120016378</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>16.15653068331635</v>
+        <v>20.97058084716383</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.680767911299174</v>
+        <v>0.5711946558878058</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.1864583541511312</v>
+        <v>1.082007190547476</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6233</v>
+        <v>6234</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>442.0695743483041</v>
+        <v>465.4414877189972</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>21.35</v>
+        <v>37.85</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>55.02064737555166</v>
+        <v>54.23099891526854</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>16.79100265835989</v>
+        <v>20.29680801630561</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6755558163131483</v>
+        <v>0.9868653522617546</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.1614099976713774</v>
+        <v>0.5286082149883267</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6418</v>
+        <v>6241</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>441.5757285346891</v>
+        <v>465.2246550354751</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>34.55</v>
+        <v>15.45</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>51.76270033930709</v>
+        <v>46.34756943664845</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>29.62341748493857</v>
+        <v>11.48368431540685</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.1094152202160514</v>
+        <v>0.9118758669782656</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.1191691627458312</v>
+        <v>-0.0664157594088272</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6188</v>
+        <v>6194</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>438.3472694522597</v>
+        <v>459.9384265565117</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>62</v>
+        <v>30.55</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>33.41576812912675</v>
+        <v>65.9119741398849</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>30.41685909605331</v>
+        <v>18.56444069773454</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.506398935503666</v>
+        <v>1.673922534946038</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0502098106937023</v>
+        <v>0.0876780506206233</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6237</v>
+        <v>6285</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>434.2211869716203</v>
+        <v>458.9103822709467</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>37</v>
+        <v>238</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,49 +3308,49 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>62.30641632927617</v>
+        <v>52.99368814470656</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>16.87008103914424</v>
+        <v>19.19277043208252</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>7.103814350115726</v>
+        <v>1.45478122683924</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M54" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.4112636293165364</v>
+        <v>1.11422738793159</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6234</v>
+        <v>6244</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>425.4414877189972</v>
+        <v>442.2937938269147</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>37.85</v>
+        <v>23.55</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>54.23099891526854</v>
+        <v>50.72279298124555</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>20.29680801630561</v>
+        <v>16.15653068331635</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9868653522617546</v>
+        <v>1.680767911299174</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.5286082149883267</v>
+        <v>0.1864583541511312</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6241</v>
+        <v>6190</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>鑫永洋</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>425.2246550354751</v>
+        <v>439.6646192834892</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>15.45</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>46.34756943664845</v>
+        <v>50.77775415430366</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>11.48368431540685</v>
+        <v>12.77166136283128</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.9118758669782656</v>
+        <v>0.4768365100193492</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.0664157594088272</v>
+        <v>0.1963630317328475</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6206</v>
+        <v>6414</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>423.036910584006</v>
+        <v>430.7072010556364</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>139</v>
+        <v>374</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,49 +3467,49 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>50.69751582163631</v>
+        <v>42.32645209555573</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>14.93495373317363</v>
+        <v>23.50530759514946</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.3883922134014348</v>
+        <v>0.6067454909135692</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M57" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.1803094862152063</v>
+        <v>1.321266692992577</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6470</v>
+        <v>6187</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>419.2708508737744</v>
+        <v>425.4533339751001</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>43</v>
+        <v>1195</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>52.14845599474718</v>
+        <v>44.71636053976056</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>23.62827772636205</v>
+        <v>13.72835710172023</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3275550635124111</v>
+        <v>0.5022947219055958</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.1311472425687095</v>
+        <v>-17.41231303596892</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6190</v>
+        <v>6417</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>399.6646192834892</v>
+        <v>419.0415423013458</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>68.59999999999999</v>
+        <v>102</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>50.77775415430366</v>
+        <v>39.45290056541137</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>12.77166136283128</v>
+        <v>38.50243124866704</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4768365100193492</v>
+        <v>1.302163926499033</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.1963630317328475</v>
+        <v>0.1976418201242129</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6187</v>
+        <v>6265</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>385.4533339751001</v>
+        <v>418.1219098785853</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>1195</v>
+        <v>48.45</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>44.71636053976056</v>
+        <v>40.50182741756877</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>13.72835710172023</v>
+        <v>20.12072849093827</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5022947219055958</v>
+        <v>0.4322829297482632</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-17.41231303596892</v>
+        <v>-0.4756110685885009</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6417</v>
+        <v>6188</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>379.0415423013458</v>
+        <v>408.3472694522597</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>39.45290056541137</v>
+        <v>33.41576812912675</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>38.50243124866704</v>
+        <v>30.41685909605331</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.302163926499033</v>
+        <v>0.506398935503666</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.1976418201242129</v>
+        <v>0.0502098106937023</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6265</v>
+        <v>6237</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>378.1219098785853</v>
+        <v>404.2211869716203</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>48.45</v>
+        <v>37</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>40.50182741756877</v>
+        <v>62.30641632927617</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>20.12072849093827</v>
+        <v>16.87008103914424</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.4322829297482632</v>
+        <v>7.103814350115726</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.4756110685885009</v>
+        <v>0.4112636293165364</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>volume_break, rsi_strong, market_above_ma60, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6261</v>
+        <v>6279</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>375.8648785599799</v>
+        <v>389.8939760574495</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>78.3</v>
+        <v>112.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>49.52662477062898</v>
+        <v>38.3786495853063</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>13.22340733910132</v>
+        <v>35.19637855007588</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.7822159383367108</v>
+        <v>0.4544712570610476</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>1</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.3924543912837848</v>
+        <v>-0.0510056578414497</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6165</v>
+        <v>6470</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>375.0194527158492</v>
+        <v>389.2708508737744</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>48.95</v>
+        <v>43</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>51.65522469823686</v>
+        <v>52.14845599474718</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>14.35776244274991</v>
+        <v>23.62827772636205</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.3204236180844755</v>
+        <v>0.3275550635124111</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.1226179575511829</v>
+        <v>0.1311472425687095</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6246</v>
+        <v>6217</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>362.5894406864204</v>
+        <v>387.6403059977919</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>12.8</v>
+        <v>170</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>49.89878723028504</v>
+        <v>49.36629716924856</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>29.50973024979936</v>
+        <v>13.30479053806468</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.1892592263872863</v>
+        <v>0.2828585845508812</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0291312053279579</v>
+        <v>-0.2515590356547658</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6183</v>
+        <v>6174</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>361.439450358852</v>
+        <v>385.9387305113407</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>91.3</v>
+        <v>44.95</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>46.2812959734157</v>
+        <v>53.04440237315566</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>12.93819719573895</v>
+        <v>13.75830600250693</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.8358651483913635</v>
+        <v>0.9214822437430756</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0415195025449918</v>
+        <v>0.2859364522273093</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6167</v>
+        <v>6206</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>360.3945452084354</v>
+        <v>383.036910584006</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>10.35</v>
+        <v>139</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>49.22656145456681</v>
+        <v>50.69751582163631</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>11.16743415879401</v>
+        <v>14.93495373317363</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.9258614980445508</v>
+        <v>0.3883922134014348</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0407918426943183</v>
+        <v>0.1803094862152063</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6263</v>
+        <v>6261</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>357.4687951312504</v>
+        <v>375.8648785599799</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>157</v>
+        <v>78.3</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>45.40923632641721</v>
+        <v>49.52662477062898</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.9994026000481</v>
+        <v>13.22340733910132</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3345619315422479</v>
+        <v>0.7822159383367108</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.4189921737297604</v>
+        <v>0.3924543912837848</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6279</v>
+        <v>6229</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>349.8939760574495</v>
+        <v>374.887673000443</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>112.5</v>
+        <v>23.7</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>38.3786495853063</v>
+        <v>51.02435900280756</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>35.19637855007588</v>
+        <v>10.51247239227078</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4544712570610476</v>
+        <v>1.787894507393719</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>1</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.0510056578414497</v>
+        <v>0.0464932614244739</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6217</v>
+        <v>6246</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>347.6403059977919</v>
+        <v>362.5894406864204</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>170</v>
+        <v>12.8</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>49.36629716924856</v>
+        <v>49.89878723028504</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>13.30479053806468</v>
+        <v>29.50973024979936</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.2828585845508812</v>
+        <v>0.1892592263872863</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.2515590356547658</v>
+        <v>0.0291312053279579</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6174</v>
+        <v>6405</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>345.9387305113407</v>
+        <v>358.3159040054463</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>44.95</v>
+        <v>41.45</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>53.04440237315566</v>
+        <v>54.4374863753659</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>13.75830600250693</v>
+        <v>22.19787641731693</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.9214822437430756</v>
+        <v>0.7982058273106563</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.2859364522273093</v>
+        <v>0.4999337154894016</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6464</v>
+        <v>6263</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>341.6280124931552</v>
+        <v>357.4687951312504</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45.31154860413452</v>
+        <v>45.40923632641721</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>21.17974310188868</v>
+        <v>15.9994026000481</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.0258545151225515</v>
+        <v>0.3345619315422479</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0017758927649053</v>
+        <v>-0.4189921737297604</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6198</v>
+        <v>6165</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>336.4797730940201</v>
+        <v>355.0194527158492</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>19.4</v>
+        <v>48.95</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>52.94284093096098</v>
+        <v>51.65522469823686</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>8.39107885512303</v>
+        <v>14.35776244274991</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5176056641686142</v>
+        <v>0.3204236180844755</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.7252487583974783</v>
+        <v>0.1226179575511829</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6229</v>
+        <v>6175</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>334.887673000443</v>
+        <v>344.6205923617438</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>23.7</v>
+        <v>69.7</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.02435900280756</v>
+        <v>41.51972468715783</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>10.51247239227078</v>
+        <v>17.27755573469414</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.787894507393719</v>
+        <v>0.4388308517117974</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>1</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0464932614244739</v>
+        <v>0.4208327072468796</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6269</v>
+        <v>6464</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>330.0840289244618</v>
+        <v>341.6280124931552</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>64.8</v>
+        <v>77</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>48.51220894355768</v>
+        <v>45.31154860413452</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.07883756773208</v>
+        <v>21.17974310188868</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.2668226654170578</v>
+        <v>0.0258545151225515</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.4559629286033612</v>
+        <v>0.0017758927649053</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6405</v>
+        <v>6183</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>328.3159040054463</v>
+        <v>341.439450358852</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>41.45</v>
+        <v>91.3</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>54.4374863753659</v>
+        <v>46.2812959734157</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>22.19787641731693</v>
+        <v>12.93819719573895</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.7982058273106563</v>
+        <v>0.8358651483913635</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.4999337154894016</v>
+        <v>-0.0415195025449918</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6451</v>
+        <v>6198</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>326.7347828857845</v>
+        <v>336.4797730940201</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>412</v>
+        <v>19.4</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>45.15748998378626</v>
+        <v>52.94284093096098</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>8.165077360048784</v>
+        <v>8.39107885512303</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.2402832464634738</v>
+        <v>0.5176056641686142</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-1.136527823731039</v>
+        <v>0.7252487583974783</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6281</v>
+        <v>6272</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>322.3023664125197</v>
+        <v>331.1287513341082</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>51</v>
+        <v>25.3</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>43.19196886924206</v>
+        <v>42.92351276222081</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>9.44472511481046</v>
+        <v>29.6378401703032</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.246051462242154</v>
+        <v>0.3033643822283974</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.0266107557776273</v>
+        <v>-0.3388584251288025</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6446</v>
+        <v>6167</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>321.8016867489027</v>
+        <v>330.3945452084354</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>1155</v>
+        <v>10.35</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>37.70268301040743</v>
+        <v>49.22656145456681</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>19.91332233501342</v>
+        <v>11.16743415879401</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.3363047400516636</v>
+        <v>0.9258614980445508</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-17.23431402341906</v>
+        <v>0.0407918426943183</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6442</v>
+        <v>6170</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>319.4928674430856</v>
+        <v>317.7149733908975</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1530</v>
+        <v>48.4</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>46.36378423009354</v>
+        <v>55.05746490579277</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>14.53493400236996</v>
+        <v>15.63255878848084</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.335084557587092</v>
+        <v>0.7633969650774827</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-23.03758894649784</v>
+        <v>-0.0125232578465917</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6175</v>
+        <v>6259</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>304.6205923617438</v>
+        <v>316.9186290747091</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>69.7</v>
+        <v>29.15</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>41.51972468715783</v>
+        <v>47.24901173244205</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>17.27755573469414</v>
+        <v>9.331955039960674</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.4388308517117974</v>
+        <v>0.1999522804176186</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.4208327072468796</v>
+        <v>0.1516932618448554</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6272</v>
+        <v>6269</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>301.1287513341082</v>
+        <v>310.0840289244618</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>25.3</v>
+        <v>64.8</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>42.92351276222081</v>
+        <v>48.51220894355768</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>29.6378401703032</v>
+        <v>13.07883756773208</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.3033643822283974</v>
+        <v>0.2668226654170578</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.3388584251288025</v>
+        <v>-0.4559629286033612</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6170</v>
+        <v>6281</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>297.7149733908975</v>
+        <v>302.3023664125197</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>48.4</v>
+        <v>51</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>55.05746490579277</v>
+        <v>43.19196886924206</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>15.63255878848084</v>
+        <v>9.44472511481046</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.7633969650774827</v>
+        <v>1.246051462242154</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0125232578465917</v>
+        <v>-0.0266107557776273</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6277</v>
+        <v>6451</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>293.1407128457347</v>
+        <v>286.7347828857845</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>77.8</v>
+        <v>412</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>47.3337223392534</v>
+        <v>45.15748998378626</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>17.1019109472108</v>
+        <v>8.165077360048784</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.4130871344689618</v>
+        <v>0.2402832464634738</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0036963857785711</v>
+        <v>-1.136527823731039</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6163</v>
+        <v>6446</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>290.4610578039632</v>
+        <v>281.8016867489027</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>41.4</v>
+        <v>1155</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>49.91367463266737</v>
+        <v>37.70268301040743</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>11.00547877705841</v>
+        <v>19.91332233501342</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.2360394854377</v>
+        <v>0.3363047400516636</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.1973740400339605</v>
+        <v>-17.23431402341906</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6191</v>
+        <v>6230</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>288.4548226217468</v>
+        <v>279.7222835757412</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>82.3</v>
+        <v>113</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>45.75095612002313</v>
+        <v>53.77027256738236</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>13.94461236375281</v>
+        <v>13.87008616732989</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.6403460571916633</v>
+        <v>0.6258834396525222</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.2965934575525913</v>
+        <v>0.4863430409939364</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6235</v>
+        <v>6442</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>286.7034726959217</v>
+        <v>279.4928674430856</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>38.7</v>
+        <v>1530</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>50.49085065345289</v>
+        <v>46.36378423009354</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>12.55513229844308</v>
+        <v>14.53493400236996</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.62343459484132</v>
+        <v>0.335084557587092</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.121360334548011</v>
+        <v>-23.03758894649784</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6449</v>
+        <v>6412</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>283.8633905955883</v>
+        <v>278.4185516522064</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>209.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>41.62341357653133</v>
+        <v>37.79188013040136</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>12.15538152877381</v>
+        <v>26.03791664100356</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.332508490117131</v>
+        <v>0.5826557882460266</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0108765456173891</v>
+        <v>0.1685064759510397</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6215</v>
+        <v>6177</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>280.3097969186821</v>
+        <v>272.3237921966169</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>96.8</v>
+        <v>46.2</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>46.09711521401546</v>
+        <v>41.60083959520327</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>10.92089897909016</v>
+        <v>17.570081989431</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.641946204768259</v>
+        <v>0.7003234123180839</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0199640007007245</v>
+        <v>-0.1415884171589934</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6230</v>
+        <v>6235</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>279.7222835757412</v>
+        <v>266.7034726959217</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>113</v>
+        <v>38.7</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>53.77027256738236</v>
+        <v>50.49085065345289</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>13.87008616732989</v>
+        <v>12.55513229844308</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.6258834396525222</v>
+        <v>1.62343459484132</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.4863430409939364</v>
+        <v>0.121360334548011</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6259</v>
+        <v>6185</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>276.9186290747091</v>
+        <v>263.5818722190636</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>29.15</v>
+        <v>12.45</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>47.24901173244205</v>
+        <v>38.9026751449344</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>9.331955039960674</v>
+        <v>25.06707504146626</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.1999522804176186</v>
+        <v>0.5733843133584536</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.1516932618448554</v>
+        <v>0.0360409966728663</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6177</v>
+        <v>6163</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>272.3237921966169</v>
+        <v>260.4610578039632</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>46.2</v>
+        <v>41.4</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>41.60083959520327</v>
+        <v>49.91367463266737</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>17.570081989431</v>
+        <v>11.00547877705841</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7003234123180839</v>
+        <v>1.2360394854377</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.1415884171589934</v>
+        <v>0.1973740400339605</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6415</v>
+        <v>6277</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>266.3991153106608</v>
+        <v>253.1407128457348</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>425.5</v>
+        <v>77.8</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,49 +5375,49 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>48.46548191839932</v>
+        <v>47.3337223392534</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>9.678042344682526</v>
+        <v>17.1019109472108</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.4839489536893613</v>
+        <v>0.4130871344689618</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>3.296308895496102</v>
+        <v>-0.0036963857785711</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6412</v>
+        <v>6191</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>248.4185516522064</v>
+        <v>248.4548226217468</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>37.79188013040136</v>
+        <v>45.75095612002313</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>26.03791664100356</v>
+        <v>13.94461236375281</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5826557882460266</v>
+        <v>0.6403460571916633</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.1685064759510397</v>
+        <v>0.2965934575525913</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6192</v>
+        <v>6449</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>241.7573065478446</v>
+        <v>243.8633905955883</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>110.5</v>
+        <v>209.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>38.96565016862916</v>
+        <v>41.62341357653133</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>27.41533889263207</v>
+        <v>12.15538152877381</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.4247648389105568</v>
+        <v>0.332508490117131</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.1428655263548504</v>
+        <v>-0.0108765456173891</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6184</v>
+        <v>6215</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>227.7043836813468</v>
+        <v>240.3097969186822</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>40.3</v>
+        <v>96.8</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>44.3078070545006</v>
+        <v>46.09711521401546</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>36.43845475996632</v>
+        <v>10.92089897909016</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.230954563436029</v>
+        <v>0.641946204768259</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.1371158929551469</v>
+        <v>0.0199640007007245</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6185</v>
+        <v>6220</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>223.5818722190636</v>
+        <v>239.0563385192113</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>12.45</v>
+        <v>25.25</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>38.9026751449344</v>
+        <v>40.34641521279349</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>25.06707504146626</v>
+        <v>10.564998027848</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5733843133584536</v>
+        <v>0.3521453903540544</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>2</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0360409966728663</v>
+        <v>0.0611514878011362</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6409</v>
+        <v>6223</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>217.8255547095952</v>
+        <v>238.3441852836838</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>879</v>
+        <v>5415</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>37.98699331430593</v>
+        <v>47.34251389087935</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>18.80190188827629</v>
+        <v>12.00169645797498</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.6084751477765469</v>
+        <v>0.5303222279471514</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-1.979010477260189</v>
+        <v>14.58219558548844</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6222</v>
+        <v>6474</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>209.6655489594881</v>
+        <v>228.0903613714612</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>18.4</v>
+        <v>35.55</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>46.75410530269195</v>
+        <v>39.89543607133883</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>4.383104653122451</v>
+        <v>15.17051919777138</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.3316587358170433</v>
+        <v>0.6861138362604273</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.1362827542410348</v>
+        <v>-0.0039333713476361</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6282</v>
+        <v>6184</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>208.9388482070138</v>
+        <v>227.7043836813468</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>42.85</v>
+        <v>40.3</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>42.02876394873476</v>
+        <v>44.3078070545006</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>17.00784694733757</v>
+        <v>36.43845475996632</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.5752956218348082</v>
+        <v>0.230954563436029</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.1880660909224483</v>
+        <v>0.1371158929551469</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6220</v>
+        <v>6415</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>199.0563385192113</v>
+        <v>226.3991153106608</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>25.25</v>
+        <v>425.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,49 +5799,49 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>40.34641521279349</v>
+        <v>48.46548191839932</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>10.564998027848</v>
+        <v>9.678042344682526</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.3521453903540544</v>
+        <v>0.4839489536893613</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0611514878011362</v>
+        <v>3.296308895496102</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6223</v>
+        <v>6283</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>198.3441852836838</v>
+        <v>222.2737447752444</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>5415</v>
+        <v>18.85</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>47.34251389087935</v>
+        <v>41.12935784356573</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>12.00169645797498</v>
+        <v>21.75920912489022</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.5303222279471514</v>
+        <v>0.2721286845972557</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>14.58219558548844</v>
+        <v>0.0308807550957894</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6283</v>
+        <v>6409</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>192.2737447752444</v>
+        <v>217.8255547095952</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>18.85</v>
+        <v>879</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>41.12935784356573</v>
+        <v>37.98699331430593</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>21.75920912489022</v>
+        <v>18.80190188827629</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.2721286845972557</v>
+        <v>0.6084751477765469</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0308807550957894</v>
+        <v>-1.979010477260189</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6474</v>
+        <v>6216</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>188.0903613714612</v>
+        <v>216.5728803333345</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>35.55</v>
+        <v>19.55</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>39.89543607133883</v>
+        <v>32.64488451358282</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>15.17051919777138</v>
+        <v>44.7997360380864</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.6861138362604273</v>
+        <v>0.2236491775487307</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0039333713476361</v>
+        <v>0.0402282387799796</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6216</v>
+        <v>6465</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>186.5728803333345</v>
+        <v>215.2652422590988</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>19.55</v>
+        <v>41.65</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>32.64488451358282</v>
+        <v>34.42493319694726</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>44.7997360380864</v>
+        <v>13.30479049546203</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.2236491775487307</v>
+        <v>0.514791135031893</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,11 +6029,11 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0402282387799796</v>
+        <v>0.0520320578724973</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>186.3717116009259</v>
+        <v>206.3717116009259</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>74.3</v>
@@ -6092,21 +6092,21 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6161</v>
+        <v>6419</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>捷波</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>185.804205017652</v>
+        <v>205.9716635143944</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>49.15</v>
+        <v>149</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>47.1279540064177</v>
+        <v>47.59814510703222</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>10.83835690120524</v>
+        <v>9.791830152220156</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.4022046388043475</v>
+        <v>0.2029733890584552</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0637214178172059</v>
+        <v>-0.4540312668936635</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6284</v>
+        <v>6192</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>182.7786128165065</v>
+        <v>201.7573065478446</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>74.3</v>
+        <v>110.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>42.57860500858608</v>
+        <v>38.96565016862916</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>7.104446471130253</v>
+        <v>27.41533889263207</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.406630448438915</v>
+        <v>0.4247648389105568</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0911280499863422</v>
+        <v>-0.1428655263548504</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6465</v>
+        <v>6284</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>175.2652422590988</v>
+        <v>182.7786128165065</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>41.65</v>
+        <v>74.3</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>34.42493319694726</v>
+        <v>42.57860500858608</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>13.30479049546203</v>
+        <v>7.104446471130253</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.514791135031893</v>
+        <v>0.406630448438915</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>1</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0520320578724973</v>
+        <v>-0.0911280499863422</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6419</v>
+        <v>6222</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>165.9716635143944</v>
+        <v>179.6655489594881</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>149</v>
+        <v>18.4</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>47.59814510703222</v>
+        <v>46.75410530269195</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>9.791830152220156</v>
+        <v>4.383104653122451</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.2029733890584552</v>
+        <v>0.3316587358170433</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.4540312668936635</v>
+        <v>-0.1362827542410348</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6203</v>
+        <v>6462</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>156.8471884399789</v>
+        <v>176.8008097181371</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>59.6</v>
+        <v>99.7</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,25 +6329,25 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>42.06665094795412</v>
+        <v>51.54621111774532</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>7.749668698014489</v>
+        <v>11.73818726756863</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.4309727197575089</v>
+        <v>0.5492099394842883</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.1108212981151282</v>
+        <v>0.2014240419835171</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>139.5218620707787</v>
+        <v>169.5218620707787</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>91.8</v>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6462</v>
+        <v>6282</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>136.8008097181372</v>
+        <v>168.9388482070138</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>99.7</v>
+        <v>42.85</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,49 +6435,49 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>51.54621111774532</v>
+        <v>42.02876394873476</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>11.73818726756863</v>
+        <v>17.00784694733757</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5492099394842883</v>
+        <v>0.5752956218348082</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L113" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M113" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.2014240419835171</v>
+        <v>0.1880660909224483</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6411</v>
+        <v>6161</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>捷波</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>127.8897659861489</v>
+        <v>155.804205017652</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>49.15</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>46.81199547150865</v>
+        <v>47.1279540064177</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>8.653018537151107</v>
+        <v>10.83835690120524</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.3360373873426625</v>
+        <v>0.4022046388043475</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>2</v>
@@ -6506,62 +6506,168 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.151267782206295</v>
+        <v>0.0637214178172059</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>晶焱</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>147.8897659861489</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>46.81199547150865</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>8.653018537151107</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.3360373873426625</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>0.151267782206295</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>海韻電</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>126.8471884399789</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>42.06665094795412</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>7.749668698014489</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.4309727197575089</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.1108212981151282</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
         <v>6276</v>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>安鈦克</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D115" s="2" t="n">
-        <v>113.9963318467911</v>
-      </c>
-      <c r="E115" s="2" t="n">
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>83.99633184679108</v>
+      </c>
+      <c r="E117" s="2" t="n">
         <v>19.65</v>
       </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H115" s="2" t="n">
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
         <v>46.72785919713524</v>
       </c>
-      <c r="I115" s="2" t="n">
+      <c r="I117" s="2" t="n">
         <v>15.56384387507603</v>
       </c>
-      <c r="J115" s="2" t="n">
+      <c r="J117" s="2" t="n">
         <v>1.242251007067564</v>
       </c>
-      <c r="K115" s="2" t="n">
+      <c r="K117" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N115" s="2" t="n">
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
         <v>-0.0022391155418597</v>
       </c>
-      <c r="O115" s="2" t="inlineStr">
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
